--- a/Versão5/SIS/Ontologia_Gases.xlsx
+++ b/Versão5/SIS/Ontologia_Gases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GASE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96289D11-A3B2-4B09-834C-C5DEF7AEB88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3339F50-34A2-46F5-8BBD-451C4365868A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1344,14 +1344,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1475,6 +1467,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1917,15 +1917,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="55" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="55" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="55"/>
+    <col min="1" max="1" width="8.69140625" style="55" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="55" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2114,19 +2114,19 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46244.675170254632</v>
+        <v>46249.440767476852</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>88</v>
       </c>
@@ -2202,35 +2202,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="53" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8" style="53" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="46.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7" style="53" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="45.140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20" style="54" customWidth="1"/>
-    <col min="26" max="26" width="7.140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="25.42578125" style="53" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="53"/>
+    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="53" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.69140625" style="53" customWidth="1"/>
+    <col min="5" max="5" width="11.69140625" style="53" customWidth="1"/>
+    <col min="6" max="6" width="11.61328125" style="61" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" style="53" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.15234375" style="53" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" style="53" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.4609375" style="53" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" style="53" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.15234375" style="53" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.3828125" style="53" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.765625" style="53" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.3828125" style="53" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.921875" style="53" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.3046875" style="53" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="41.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.23046875" style="54" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.07421875" style="53" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="29.23046875" style="53" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="42.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>93</v>
       </c>
@@ -2313,7 +2312,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -2402,7 +2401,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -2491,7 +2490,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -2580,7 +2579,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -2669,7 +2668,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -2758,7 +2757,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -2847,7 +2846,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -2936,7 +2935,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -3025,7 +3024,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -3114,7 +3113,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -3292,7 +3291,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -3381,7 +3380,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -3470,7 +3469,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -3559,7 +3558,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -3648,7 +3647,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -3737,7 +3736,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -3826,7 +3825,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="57">
         <v>19</v>
       </c>
@@ -3915,7 +3914,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="57">
         <v>20</v>
       </c>
@@ -4004,7 +4003,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="57">
         <v>21</v>
       </c>
@@ -4093,7 +4092,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="57">
         <v>22</v>
       </c>
@@ -4182,7 +4181,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="57">
         <v>23</v>
       </c>
@@ -4271,7 +4270,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="57">
         <v>24</v>
       </c>
@@ -4360,7 +4359,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="57">
         <v>25</v>
       </c>
@@ -4454,29 +4453,32 @@
     <sortCondition ref="F2:F886"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA2:AA25 A2:B25">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B25 AA2:AA25">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:D1 F1:O1 R1:X1 Z1:AA1">
-    <cfRule type="cellIs" dxfId="15" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="55" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="14" priority="1491"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F1048576 F1:F2">
-    <cfRule type="duplicateValues" dxfId="13" priority="1513"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26:F1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1463"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1484"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1463"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1484"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -4484,15 +4486,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -4557,7 +4559,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -4622,7 +4624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -4689,7 +4691,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4705,29 +4707,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
-    <col min="4" max="5" width="7.140625" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" customWidth="1"/>
-    <col min="7" max="7" width="67.85546875" customWidth="1"/>
-    <col min="8" max="8" width="5.28515625" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.42578125" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.42578125" customWidth="1"/>
-    <col min="16" max="16" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.07421875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.61328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="62" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.23046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.07421875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.23046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.61328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.15234375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.23046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -4786,7 +4789,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>1</v>
       </c>
@@ -4845,7 +4848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>2</v>
       </c>
@@ -4904,7 +4907,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>3</v>
       </c>
@@ -4963,7 +4966,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>4</v>
       </c>
@@ -5025,7 +5028,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="7" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1495"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5035,15 +5038,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -5066,7 +5069,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -5095,22 +5098,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Gases.xlsx
+++ b/Versão5/SIS/Ontologia_Gases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3339F50-34A2-46F5-8BBD-451C4365868A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708702A8-D185-454C-8B02-3CB3ECB194B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="247">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -321,12 +321,6 @@
     <t>é.dentro.de</t>
   </si>
   <si>
-    <t>CategoriaRvt</t>
-  </si>
-  <si>
-    <t>ClasseIfc</t>
-  </si>
-  <si>
     <t>ABNT</t>
   </si>
   <si>
@@ -804,6 +798,21 @@
   </si>
   <si>
     <t>"Indivíduo que representa um sistema de Gás doméstico"</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
+  </si>
+  <si>
+    <t>Categoria Rvt</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
   </si>
 </sst>
 </file>
@@ -1333,7 +1342,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
     <dxf>
       <font>
         <b val="0"/>
@@ -1406,6 +1415,14 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -1933,7 +1950,7 @@
         <v>45</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1944,7 +1961,7 @@
         <v>47</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1952,10 +1969,10 @@
         <v>48</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1966,7 +1983,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1978,7 +1995,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1990,7 +2007,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2001,7 +2018,7 @@
         <v>53</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2009,10 +2026,10 @@
         <v>54</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2023,7 +2040,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2034,7 +2051,7 @@
         <v>58</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2045,7 +2062,7 @@
         <v>58</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2056,7 +2073,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2067,7 +2084,7 @@
         <v>58</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2078,7 +2095,7 @@
         <v>58</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2089,7 +2106,7 @@
         <v>58</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2100,7 +2117,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2108,10 +2125,10 @@
         <v>65</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2120,10 +2137,10 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46249.440767476852</v>
+        <v>46253.81311516204</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2134,7 +2151,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2145,7 +2162,7 @@
         <v>58</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2156,7 +2173,7 @@
         <v>58</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2164,10 +2181,10 @@
         <v>71</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2175,22 +2192,22 @@
         <v>72</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B24" s="16" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific Household and Hospital Gas Objects</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2201,7 +2218,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
@@ -2216,22 +2233,24 @@
     <col min="15" max="15" width="11" style="53" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="32.69140625" style="53" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="34.15234375" style="53" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.3828125" style="53" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.765625" style="53" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.3828125" style="53" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.921875" style="53" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.3046875" style="53" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="41.69140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.23046875" style="54" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.07421875" style="53" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="29.23046875" style="53" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="53"/>
+    <col min="18" max="18" width="29.23046875" style="53" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.3828125" style="53" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.765625" style="53" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.3828125" style="53" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.921875" style="53" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.3046875" style="53" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="41.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.07421875" style="53" customWidth="1"/>
+    <col min="27" max="27" width="17.23046875" style="54" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.07421875" style="53" customWidth="1"/>
+    <col min="29" max="29" width="5.07421875" style="53" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="42.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="42.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B1" s="44" t="s">
         <v>42</v>
@@ -2264,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M1" s="35" t="s">
         <v>5</v>
@@ -2281,55 +2300,61 @@
       <c r="Q1" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="35" t="s">
-        <v>95</v>
+      <c r="R1" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="S1" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="T1" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="35" t="s">
+      <c r="U1" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="46" t="s">
+      <c r="V1" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="35" t="s">
+      <c r="W1" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="59" t="s">
+      <c r="X1" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="35" t="s">
+      <c r="Y1" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="Z1" s="35" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA1" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB1" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC1" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="Y1" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z1" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA1" s="36" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="57">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G2" s="60" t="s">
         <v>9</v>
@@ -2363,62 +2388,68 @@
         <v>Sistema.GAS</v>
       </c>
       <c r="P2" s="52" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q2" s="52" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="R2" s="30" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="S2" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T2" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U2" s="30" t="str">
-        <f t="shared" ref="U2:U20" si="4">SUBSTITUTE(E2, "_", " ")</f>
+        <v>152</v>
+      </c>
+      <c r="U2" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V2" s="30" t="str">
+        <f t="shared" ref="V2:V20" si="4">SUBSTITUTE(E2, "_", " ")</f>
         <v>Sistema.de.Gás</v>
       </c>
-      <c r="V2" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W2" s="58" t="str">
-        <f t="shared" ref="W2:W25" si="5">CONCATENATE("Key-GAS-",A2)</f>
+      <c r="W2" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X2" s="58" t="str">
+        <f t="shared" ref="X2:X25" si="5">CONCATENATE("Key-GAS-",A2)</f>
         <v>Key-GAS-2</v>
       </c>
-      <c r="X2" s="29" t="s">
-        <v>110</v>
-      </c>
       <c r="Y2" s="29" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="Z2" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA2" s="30" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA2" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB2" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC2" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="57">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F3" s="56" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G3" s="60" t="s">
         <v>9</v>
@@ -2452,62 +2483,68 @@
         <v>Sistema.Oxigênio</v>
       </c>
       <c r="P3" s="52" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Q3" s="52" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R3" s="30" t="s">
-        <v>9</v>
+        <v>203</v>
       </c>
       <c r="S3" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T3" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U3" s="30" t="str">
-        <f t="shared" ref="U3:U14" si="9">SUBSTITUTE(E3, "_", " ")</f>
+        <v>152</v>
+      </c>
+      <c r="U3" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V3" s="30" t="str">
+        <f t="shared" ref="V3:V14" si="9">SUBSTITUTE(E3, "_", " ")</f>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
-      <c r="V3" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W3" s="58" t="str">
+      <c r="W3" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X3" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-3</v>
       </c>
-      <c r="X3" s="29" t="s">
-        <v>110</v>
-      </c>
       <c r="Y3" s="29" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="Z3" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA3" s="30" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA3" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB3" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC3" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="57">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G4" s="60" t="s">
         <v>9</v>
@@ -2541,62 +2578,68 @@
         <v>Sistema.Ar.Medicinal</v>
       </c>
       <c r="P4" s="52" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q4" s="52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R4" s="30" t="s">
-        <v>9</v>
+        <v>204</v>
       </c>
       <c r="S4" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T4" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U4" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U4" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V4" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
-      <c r="V4" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W4" s="58" t="str">
+      <c r="W4" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X4" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-4</v>
       </c>
-      <c r="X4" s="29" t="s">
-        <v>110</v>
-      </c>
       <c r="Y4" s="29" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="Z4" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA4" s="30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA4" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB4" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC4" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="57">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G5" s="60" t="s">
         <v>9</v>
@@ -2630,62 +2673,68 @@
         <v>Sistema.Ar.Comprimido</v>
       </c>
       <c r="P5" s="52" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q5" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="R5" s="30" t="s">
-        <v>9</v>
+        <v>205</v>
       </c>
       <c r="S5" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U5" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U5" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V5" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
-      <c r="V5" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W5" s="58" t="str">
+      <c r="W5" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X5" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-5</v>
       </c>
-      <c r="X5" s="29" t="s">
-        <v>110</v>
-      </c>
       <c r="Y5" s="29" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA5" s="30" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA5" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB5" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC5" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="57">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G6" s="60" t="s">
         <v>9</v>
@@ -2719,62 +2768,68 @@
         <v>Sistema.Óxido.Nitroso</v>
       </c>
       <c r="P6" s="52" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q6" s="52" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="R6" s="30" t="s">
-        <v>9</v>
+        <v>206</v>
       </c>
       <c r="S6" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T6" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U6" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U6" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
-      <c r="V6" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W6" s="58" t="str">
+      <c r="W6" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X6" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-6</v>
       </c>
-      <c r="X6" s="29" t="s">
-        <v>110</v>
-      </c>
       <c r="Y6" s="29" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="Z6" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA6" s="30" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA6" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB6" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC6" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="57">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F7" s="56" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G7" s="60" t="s">
         <v>9</v>
@@ -2808,62 +2863,68 @@
         <v>Sistema.Nitrogênio</v>
       </c>
       <c r="P7" s="52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Q7" s="52" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="R7" s="30" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="S7" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T7" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U7" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U7" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V7" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
-      <c r="V7" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W7" s="58" t="str">
+      <c r="W7" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X7" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-7</v>
       </c>
-      <c r="X7" s="29" t="s">
-        <v>110</v>
-      </c>
       <c r="Y7" s="29" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="Z7" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA7" s="30" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA7" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB7" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC7" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="57">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G8" s="60" t="s">
         <v>9</v>
@@ -2897,62 +2958,68 @@
         <v>Sistema.Hélio</v>
       </c>
       <c r="P8" s="52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q8" s="52" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="R8" s="30" t="s">
-        <v>9</v>
+        <v>208</v>
       </c>
       <c r="S8" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U8" s="30" t="str">
-        <f t="shared" ref="U8" si="13">SUBSTITUTE(E8, "_", " ")</f>
+        <v>152</v>
+      </c>
+      <c r="U8" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V8" s="30" t="str">
+        <f t="shared" ref="V8" si="13">SUBSTITUTE(E8, "_", " ")</f>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
-      <c r="V8" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W8" s="58" t="str">
+      <c r="W8" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X8" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-8</v>
       </c>
-      <c r="X8" s="29" t="s">
-        <v>110</v>
-      </c>
       <c r="Y8" s="29" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA8" s="30" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA8" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB8" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC8" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="57">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G9" s="60" t="s">
         <v>9</v>
@@ -2986,62 +3053,68 @@
         <v>Sistema.Vacuo</v>
       </c>
       <c r="P9" s="52" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Q9" s="52" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>9</v>
+        <v>209</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T9" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U9" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V9" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
-      <c r="V9" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W9" s="58" t="str">
+      <c r="W9" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X9" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-9</v>
       </c>
-      <c r="X9" s="29" t="s">
-        <v>110</v>
-      </c>
       <c r="Y9" s="29" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="Z9" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA9" s="30" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA9" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB9" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC9" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="57">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G10" s="60" t="s">
         <v>9</v>
@@ -3075,62 +3148,68 @@
         <v>Queimador</v>
       </c>
       <c r="P10" s="52" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q10" s="52" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R10" s="30" t="s">
-        <v>9</v>
+        <v>210</v>
       </c>
       <c r="S10" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T10" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U10" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U10" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V10" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V10" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W10" s="58" t="str">
+      <c r="W10" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X10" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-10</v>
       </c>
-      <c r="X10" s="29" t="s">
-        <v>156</v>
-      </c>
       <c r="Y10" s="29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Z10" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA10" s="30" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA10" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="AB10" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC10" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="57">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G11" s="60" t="s">
         <v>9</v>
@@ -3164,62 +3243,68 @@
         <v>Registro.de.Gás</v>
       </c>
       <c r="P11" s="52" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q11" s="52" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R11" s="30" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="S11" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T11" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U11" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U11" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V11" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V11" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W11" s="58" t="str">
+      <c r="W11" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X11" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-11</v>
       </c>
-      <c r="X11" s="29" t="s">
-        <v>156</v>
-      </c>
       <c r="Y11" s="29" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="Z11" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA11" s="30" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA11" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB11" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC11" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="57">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G12" s="60" t="s">
         <v>9</v>
@@ -3253,62 +3338,68 @@
         <v>Válvula.de.Gás</v>
       </c>
       <c r="P12" s="52" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Q12" s="52" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="R12" s="30" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="S12" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T12" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U12" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U12" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V12" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V12" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W12" s="58" t="str">
+      <c r="W12" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X12" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-12</v>
       </c>
-      <c r="X12" s="29" t="s">
-        <v>156</v>
-      </c>
       <c r="Y12" s="29" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="Z12" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA12" s="30" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA12" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB12" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC12" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="57">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G13" s="60" t="s">
         <v>9</v>
@@ -3342,62 +3433,68 @@
         <v>Medidor.de.Gás</v>
       </c>
       <c r="P13" s="52" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q13" s="52" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="R13" s="30" t="s">
-        <v>9</v>
+        <v>213</v>
       </c>
       <c r="S13" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T13" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U13" s="30" t="str">
-        <f t="shared" ref="U13" si="18">SUBSTITUTE(E13, "_", " ")</f>
+        <v>152</v>
+      </c>
+      <c r="U13" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V13" s="30" t="str">
+        <f t="shared" ref="V13" si="18">SUBSTITUTE(E13, "_", " ")</f>
         <v>Peças.Gás</v>
       </c>
-      <c r="V13" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W13" s="58" t="str">
+      <c r="W13" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X13" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-13</v>
       </c>
-      <c r="X13" s="29" t="s">
-        <v>156</v>
-      </c>
       <c r="Y13" s="29" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="Z13" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA13" s="30" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA13" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="AB13" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC13" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="57">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E14" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G14" s="60" t="s">
         <v>9</v>
@@ -3431,62 +3528,68 @@
         <v>Acessório.de.Gás</v>
       </c>
       <c r="P14" s="52" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Q14" s="52" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R14" s="30" t="s">
-        <v>9</v>
+        <v>214</v>
       </c>
       <c r="S14" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T14" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U14" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U14" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V14" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V14" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W14" s="58" t="str">
+      <c r="W14" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X14" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-14</v>
       </c>
-      <c r="X14" s="29" t="s">
-        <v>235</v>
-      </c>
       <c r="Y14" s="29" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="Z14" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA14" s="30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA14" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB14" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC14" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="57">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E15" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F15" s="42" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G15" s="60" t="s">
         <v>9</v>
@@ -3520,62 +3623,68 @@
         <v>Buchão.de.Gás</v>
       </c>
       <c r="P15" s="52" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q15" s="52" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="R15" s="30" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="S15" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T15" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U15" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U15" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V15" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V15" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W15" s="58" t="str">
+      <c r="W15" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X15" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-15</v>
       </c>
-      <c r="X15" s="29" t="s">
-        <v>240</v>
-      </c>
       <c r="Y15" s="29" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="Z15" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA15" s="30" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA15" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB15" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC15" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="57">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E16" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="42" t="s">
         <v>119</v>
-      </c>
-      <c r="F16" s="42" t="s">
-        <v>121</v>
       </c>
       <c r="G16" s="60" t="s">
         <v>9</v>
@@ -3609,62 +3718,68 @@
         <v>Cilindro.de.Gás</v>
       </c>
       <c r="P16" s="52" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q16" s="52" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R16" s="30" t="s">
-        <v>9</v>
+        <v>215</v>
       </c>
       <c r="S16" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T16" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U16" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U16" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V16" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V16" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W16" s="58" t="str">
+      <c r="W16" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X16" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-16</v>
       </c>
-      <c r="X16" s="29" t="s">
-        <v>240</v>
-      </c>
       <c r="Y16" s="29" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="Z16" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA16" s="30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA16" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB16" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC16" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="57">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F17" s="42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G17" s="60" t="s">
         <v>9</v>
@@ -3698,62 +3813,68 @@
         <v>Tanque.de.Gás</v>
       </c>
       <c r="P17" s="52" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q17" s="52" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="R17" s="30" t="s">
-        <v>9</v>
+        <v>216</v>
       </c>
       <c r="S17" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T17" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U17" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U17" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V17" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V17" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W17" s="58" t="str">
+      <c r="W17" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X17" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-17</v>
       </c>
-      <c r="X17" s="29" t="s">
-        <v>240</v>
-      </c>
       <c r="Y17" s="29" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="Z17" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA17" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA17" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB17" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC17" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="57">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F18" s="42" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G18" s="60" t="s">
         <v>9</v>
@@ -3787,62 +3908,68 @@
         <v>Aquecedor.a.Gás</v>
       </c>
       <c r="P18" s="52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q18" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="R18" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="S18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="R18" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="T18" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U18" s="30" t="str">
+      <c r="U18" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V18" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Gás.Doméstico</v>
       </c>
-      <c r="V18" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W18" s="58" t="str">
+      <c r="W18" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X18" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-18</v>
       </c>
-      <c r="X18" s="29" t="s">
-        <v>156</v>
-      </c>
       <c r="Y18" s="29" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="Z18" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA18" s="30" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA18" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB18" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC18" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="57">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E19" s="42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F19" s="42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G19" s="60" t="s">
         <v>9</v>
@@ -3876,62 +4003,68 @@
         <v>Boiler.a.Gás</v>
       </c>
       <c r="P19" s="52" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q19" s="52" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="R19" s="30" t="s">
-        <v>9</v>
+        <v>219</v>
       </c>
       <c r="S19" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T19" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U19" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U19" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V19" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Gás.Doméstico</v>
       </c>
-      <c r="V19" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W19" s="58" t="str">
+      <c r="W19" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X19" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-19</v>
       </c>
-      <c r="X19" s="29" t="s">
-        <v>156</v>
-      </c>
       <c r="Y19" s="29" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="Z19" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA19" s="30" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA19" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB19" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC19" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="57">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E20" s="42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G20" s="60" t="s">
         <v>9</v>
@@ -3965,62 +4098,68 @@
         <v>Caldeira.a.Gás</v>
       </c>
       <c r="P20" s="52" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q20" s="52" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R20" s="30" t="s">
-        <v>9</v>
+        <v>229</v>
       </c>
       <c r="S20" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T20" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U20" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U20" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V20" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Gás.Doméstico</v>
       </c>
-      <c r="V20" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W20" s="58" t="str">
+      <c r="W20" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X20" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-20</v>
       </c>
-      <c r="X20" s="29" t="s">
-        <v>156</v>
-      </c>
       <c r="Y20" s="29" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="Z20" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA20" s="30" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA20" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB20" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC20" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="57">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G21" s="60" t="s">
         <v>9</v>
@@ -4054,62 +4193,68 @@
         <v>Tubulação.Gás</v>
       </c>
       <c r="P21" s="52" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q21" s="52" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R21" s="30" t="s">
-        <v>9</v>
+        <v>217</v>
       </c>
       <c r="S21" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T21" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U21" s="30" t="str">
-        <f t="shared" ref="U21" si="23">SUBSTITUTE(E21, "_", " ")</f>
+        <v>152</v>
+      </c>
+      <c r="U21" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V21" s="30" t="str">
+        <f t="shared" ref="V21" si="23">SUBSTITUTE(E21, "_", " ")</f>
         <v>Gás.Doméstico</v>
       </c>
-      <c r="V21" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W21" s="58" t="str">
+      <c r="W21" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X21" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-21</v>
       </c>
-      <c r="X21" s="29" t="s">
-        <v>240</v>
-      </c>
       <c r="Y21" s="29" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Z21" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA21" s="30" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA21" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="AB21" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC21" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="57">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G22" s="60" t="s">
         <v>9</v>
@@ -4143,62 +4288,68 @@
         <v>Aquecedor.a.Gás.Hospitalar</v>
       </c>
       <c r="P22" s="52" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Q22" s="52" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R22" s="30" t="s">
-        <v>9</v>
+        <v>221</v>
       </c>
       <c r="S22" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T22" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U22" s="30" t="str">
-        <f t="shared" ref="U22:U24" si="27">SUBSTITUTE(E22, "_", " ")</f>
+        <v>152</v>
+      </c>
+      <c r="U22" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V22" s="30" t="str">
+        <f t="shared" ref="V22:V24" si="27">SUBSTITUTE(E22, "_", " ")</f>
         <v>Gás.Hospitalar</v>
       </c>
-      <c r="V22" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W22" s="58" t="str">
+      <c r="W22" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X22" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-22</v>
       </c>
-      <c r="X22" s="29" t="s">
-        <v>156</v>
-      </c>
       <c r="Y22" s="29" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="Z22" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA22" s="30" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA22" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB22" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC22" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="57">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F23" s="42" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G23" s="60" t="s">
         <v>9</v>
@@ -4232,62 +4383,68 @@
         <v>Boiler.a.Gás.Hospitalar</v>
       </c>
       <c r="P23" s="52" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="Q23" s="52" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="R23" s="30" t="s">
-        <v>9</v>
+        <v>222</v>
       </c>
       <c r="S23" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T23" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U23" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U23" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V23" s="30" t="str">
         <f t="shared" si="27"/>
         <v>Gás.Hospitalar</v>
       </c>
-      <c r="V23" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W23" s="58" t="str">
+      <c r="W23" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X23" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-23</v>
       </c>
-      <c r="X23" s="29" t="s">
-        <v>156</v>
-      </c>
       <c r="Y23" s="29" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="Z23" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA23" s="30" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA23" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB23" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC23" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="57">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G24" s="60" t="s">
         <v>9</v>
@@ -4321,62 +4478,68 @@
         <v>Caldeira.a.Gás.Hospitalar</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Q24" s="52" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="R24" s="30" t="s">
-        <v>9</v>
+        <v>228</v>
       </c>
       <c r="S24" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T24" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U24" s="30" t="str">
+        <v>152</v>
+      </c>
+      <c r="U24" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V24" s="30" t="str">
         <f t="shared" si="27"/>
         <v>Gás.Hospitalar</v>
       </c>
-      <c r="V24" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W24" s="58" t="str">
+      <c r="W24" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X24" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-24</v>
       </c>
-      <c r="X24" s="29" t="s">
-        <v>156</v>
-      </c>
       <c r="Y24" s="29" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="Z24" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA24" s="30" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+      <c r="AA24" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB24" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC24" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="57">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G25" s="60" t="s">
         <v>9</v>
@@ -4410,70 +4573,81 @@
         <v>Tubulação.Gás.Hospitalar</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Q25" s="52" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="R25" s="30" t="s">
-        <v>9</v>
+        <v>220</v>
       </c>
       <c r="S25" s="30" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="T25" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="U25" s="30" t="str">
-        <f t="shared" ref="U25" si="32">SUBSTITUTE(E25, "_", " ")</f>
+        <v>152</v>
+      </c>
+      <c r="U25" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V25" s="30" t="str">
+        <f t="shared" ref="V25" si="32">SUBSTITUTE(E25, "_", " ")</f>
         <v>Gás.Hospitalar</v>
       </c>
-      <c r="V25" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="W25" s="58" t="str">
+      <c r="W25" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X25" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GAS-25</v>
       </c>
-      <c r="X25" s="29" t="s">
-        <v>240</v>
-      </c>
       <c r="Y25" s="29" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Z25" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA25" s="30" t="s">
-        <v>222</v>
+        <v>243</v>
+      </c>
+      <c r="AA25" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="AB25" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC25" s="30" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA886">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC886">
     <sortCondition ref="F2:F886"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B25 AA2:AA25">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B25">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:D1 F1:O1 R1:X1 Z1:AA1">
-    <cfRule type="cellIs" dxfId="14" priority="55" operator="equal">
+  <conditionalFormatting sqref="A1:D1 F1:O1 AB1:AC1 R1:Z1">
+    <cfRule type="cellIs" dxfId="15" priority="56" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="13" priority="1491"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F1048576 F1:F2">
-    <cfRule type="duplicateValues" dxfId="12" priority="1513"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26:F1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1463"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="1484"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1464"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1485"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R25">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -4794,10 +4968,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D2" s="50" t="s">
         <v>9</v>
@@ -4809,7 +4983,7 @@
         <v>77</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H2" s="49" t="s">
         <v>9</v>
@@ -4853,28 +5027,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>82</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H3" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J3" s="49" t="s">
         <v>9</v>
@@ -4904,7 +5078,7 @@
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -4912,22 +5086,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H4" s="49" t="s">
         <v>9</v>
@@ -4936,34 +5110,34 @@
         <v>9</v>
       </c>
       <c r="J4" s="49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L4" s="49" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M4" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N4" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="P4" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="R4" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N4" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="P4" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="R4" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="S4" s="24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -4971,22 +5145,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>9</v>
@@ -4995,34 +5169,34 @@
         <v>9</v>
       </c>
       <c r="J5" s="49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K5" s="24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L5" s="49" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M5" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N5" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="P5" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q5" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="R5" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N5" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="P5" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q5" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="R5" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="S5" s="24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Versão5/SIS/Ontologia_Gases.xlsx
+++ b/Versão5/SIS/Ontologia_Gases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708702A8-D185-454C-8B02-3CB3ECB194B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D769D0-CB87-44DC-A1B9-0DE7CE4AC116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="252">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -803,9 +803,6 @@
     <t>Atributo IFC</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Categoria Rvt</t>
   </si>
   <si>
@@ -813,6 +810,24 @@
   </si>
   <si>
     <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
   </si>
 </sst>
 </file>
@@ -903,7 +918,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1042,6 +1057,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1155,7 +1176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1336,13 +1357,134 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1484,14 +1626,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1934,15 +2068,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="55" customWidth="1"/>
-    <col min="2" max="2" width="40.15234375" style="55" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="55"/>
+    <col min="1" max="1" width="8.7109375" style="55" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="55" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -1953,7 +2087,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -1964,7 +2098,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -1975,7 +2109,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -1986,7 +2120,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -1998,7 +2132,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2010,7 +2144,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2021,7 +2155,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2032,7 +2166,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2043,7 +2177,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2054,7 +2188,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2065,7 +2199,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2076,7 +2210,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2087,7 +2221,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2098,7 +2232,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2109,7 +2243,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2120,7 +2254,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2131,19 +2265,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46253.81311516204</v>
+        <v>46260.364439351855</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2154,7 +2288,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2165,7 +2299,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2176,7 +2310,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2187,7 +2321,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2198,7 +2332,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>86</v>
       </c>
@@ -2218,37 +2352,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC25"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC26"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="53" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7.69140625" style="53" customWidth="1"/>
-    <col min="5" max="5" width="11.69140625" style="53" customWidth="1"/>
-    <col min="6" max="6" width="11.61328125" style="61" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="53" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.15234375" style="53" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7" style="53" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.4609375" style="53" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11" style="53" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.69140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="34.15234375" style="53" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.23046875" style="53" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.3828125" style="53" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.765625" style="53" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.3828125" style="53" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.921875" style="53" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.3046875" style="53" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="41.69140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.07421875" style="53" customWidth="1"/>
-    <col min="27" max="27" width="17.23046875" style="54" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.07421875" style="53" customWidth="1"/>
-    <col min="29" max="29" width="5.07421875" style="53" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="53"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.85546875" style="53" customWidth="1"/>
+    <col min="12" max="12" width="10" style="53" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="40.28515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="55.42578125" style="53" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17" style="54" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="42.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
         <v>91</v>
       </c>
@@ -2322,13 +2457,13 @@
         <v>8</v>
       </c>
       <c r="Y1" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z1" s="35" t="s">
         <v>244</v>
       </c>
-      <c r="Z1" s="35" t="s">
+      <c r="AA1" s="35" t="s">
         <v>245</v>
-      </c>
-      <c r="AA1" s="35" t="s">
-        <v>246</v>
       </c>
       <c r="AB1" s="35" t="s">
         <v>242</v>
@@ -2337,7 +2472,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -2413,26 +2548,26 @@
         <v>102</v>
       </c>
       <c r="X2" s="58" t="str">
-        <f t="shared" ref="X2:X25" si="5">CONCATENATE("Key-GAS-",A2)</f>
+        <f t="shared" ref="X2:X26" si="5">CONCATENATE("Key-GAS-",A2)</f>
         <v>Key-GAS-2</v>
       </c>
       <c r="Y2" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z2" s="30" t="s">
-        <v>243</v>
+      <c r="Z2" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA2" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB2" s="30" t="s">
-        <v>243</v>
+      <c r="AB2" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -2514,20 +2649,20 @@
       <c r="Y3" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z3" s="30" t="s">
-        <v>243</v>
+      <c r="Z3" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA3" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB3" s="30" t="s">
-        <v>243</v>
+      <c r="AB3" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -2609,20 +2744,20 @@
       <c r="Y4" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z4" s="30" t="s">
-        <v>243</v>
+      <c r="Z4" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA4" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB4" s="30" t="s">
-        <v>243</v>
+      <c r="AB4" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -2704,20 +2839,20 @@
       <c r="Y5" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z5" s="30" t="s">
-        <v>243</v>
+      <c r="Z5" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA5" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="AB5" s="30" t="s">
-        <v>243</v>
+      <c r="AB5" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -2799,20 +2934,20 @@
       <c r="Y6" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z6" s="30" t="s">
-        <v>243</v>
+      <c r="Z6" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA6" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB6" s="30" t="s">
-        <v>243</v>
+      <c r="AB6" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -2894,20 +3029,20 @@
       <c r="Y7" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z7" s="30" t="s">
-        <v>243</v>
+      <c r="Z7" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA7" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB7" s="30" t="s">
-        <v>243</v>
+      <c r="AB7" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -2989,20 +3124,20 @@
       <c r="Y8" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z8" s="30" t="s">
-        <v>243</v>
+      <c r="Z8" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA8" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB8" s="30" t="s">
-        <v>243</v>
+      <c r="AB8" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -3084,20 +3219,20 @@
       <c r="Y9" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z9" s="30" t="s">
-        <v>243</v>
+      <c r="Z9" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA9" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="AB9" s="30" t="s">
-        <v>243</v>
+      <c r="AB9" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -3179,20 +3314,20 @@
       <c r="Y10" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z10" s="30" t="s">
-        <v>243</v>
+      <c r="Z10" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA10" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="AB10" s="30" t="s">
-        <v>243</v>
+      <c r="AB10" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -3274,20 +3409,20 @@
       <c r="Y11" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z11" s="30" t="s">
-        <v>243</v>
+      <c r="Z11" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA11" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="AB11" s="30" t="s">
-        <v>243</v>
+      <c r="AB11" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -3369,20 +3504,20 @@
       <c r="Y12" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z12" s="30" t="s">
-        <v>243</v>
+      <c r="Z12" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA12" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="AB12" s="30" t="s">
-        <v>243</v>
+      <c r="AB12" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -3464,20 +3599,20 @@
       <c r="Y13" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z13" s="30" t="s">
-        <v>243</v>
+      <c r="Z13" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="AB13" s="30" t="s">
-        <v>243</v>
+      <c r="AB13" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -3559,20 +3694,20 @@
       <c r="Y14" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="Z14" s="30" t="s">
-        <v>243</v>
+      <c r="Z14" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="AB14" s="30" t="s">
-        <v>243</v>
+      <c r="AB14" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -3654,20 +3789,20 @@
       <c r="Y15" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="Z15" s="30" t="s">
-        <v>243</v>
+      <c r="Z15" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB15" s="30" t="s">
-        <v>243</v>
+      <c r="AB15" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -3749,20 +3884,20 @@
       <c r="Y16" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="Z16" s="30" t="s">
-        <v>243</v>
+      <c r="Z16" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB16" s="30" t="s">
-        <v>243</v>
+      <c r="AB16" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -3844,20 +3979,20 @@
       <c r="Y17" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="Z17" s="30" t="s">
-        <v>243</v>
+      <c r="Z17" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB17" s="30" t="s">
-        <v>243</v>
+      <c r="AB17" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -3939,20 +4074,20 @@
       <c r="Y18" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z18" s="30" t="s">
-        <v>243</v>
+      <c r="Z18" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB18" s="30" t="s">
-        <v>243</v>
+      <c r="AB18" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="57">
         <v>19</v>
       </c>
@@ -4034,20 +4169,20 @@
       <c r="Y19" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z19" s="30" t="s">
-        <v>243</v>
+      <c r="Z19" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB19" s="30" t="s">
-        <v>243</v>
+      <c r="AB19" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="57">
         <v>20</v>
       </c>
@@ -4129,20 +4264,20 @@
       <c r="Y20" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z20" s="30" t="s">
-        <v>243</v>
+      <c r="Z20" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="AB20" s="30" t="s">
-        <v>243</v>
+      <c r="AB20" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="57">
         <v>21</v>
       </c>
@@ -4224,20 +4359,20 @@
       <c r="Y21" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="Z21" s="30" t="s">
-        <v>243</v>
+      <c r="Z21" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA21" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="AB21" s="30" t="s">
-        <v>243</v>
+      <c r="AB21" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC21" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="57">
         <v>22</v>
       </c>
@@ -4319,20 +4454,20 @@
       <c r="Y22" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z22" s="30" t="s">
-        <v>243</v>
+      <c r="Z22" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA22" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB22" s="30" t="s">
-        <v>243</v>
+      <c r="AB22" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC22" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="57">
         <v>23</v>
       </c>
@@ -4414,20 +4549,20 @@
       <c r="Y23" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z23" s="30" t="s">
-        <v>243</v>
+      <c r="Z23" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA23" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB23" s="30" t="s">
-        <v>243</v>
+      <c r="AB23" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC23" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="57">
         <v>24</v>
       </c>
@@ -4509,20 +4644,20 @@
       <c r="Y24" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z24" s="30" t="s">
-        <v>243</v>
+      <c r="Z24" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA24" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="AB24" s="30" t="s">
-        <v>243</v>
+      <c r="AB24" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC24" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="57">
         <v>25</v>
       </c>
@@ -4604,17 +4739,116 @@
       <c r="Y25" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="Z25" s="30" t="s">
-        <v>243</v>
+      <c r="Z25" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AA25" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="AB25" s="30" t="s">
-        <v>243</v>
+      <c r="AB25" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AC25" s="30" t="s">
         <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="57">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" s="66" t="s">
+        <v>247</v>
+      </c>
+      <c r="D26" s="66" t="s">
+        <v>248</v>
+      </c>
+      <c r="E26" s="66" t="s">
+        <v>249</v>
+      </c>
+      <c r="F26" s="66" t="s">
+        <v>250</v>
+      </c>
+      <c r="G26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L26" s="33" t="str">
+        <f t="shared" ref="L26:O26" si="33">SUBSTITUTE(CONCATENATE("", C26), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M26" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N26" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Macros</v>
+      </c>
+      <c r="O26" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P26" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q26" s="62" t="str">
+        <f t="shared" ref="Q26" si="34">_xlfn.TRANSLATE(P26,"pt","es")</f>
+        <v>Aplicación Revit</v>
+      </c>
+      <c r="R26" s="62" t="str">
+        <f t="shared" ref="R26" si="35">_xlfn.TRANSLATE(P26,"pt","en")</f>
+        <v>Revit App</v>
+      </c>
+      <c r="S26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T26" s="30" t="str">
+        <f t="shared" ref="T26:V26" si="36">SUBSTITUTE(C26, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U26" s="30" t="str">
+        <f t="shared" si="36"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V26" s="63" t="str">
+        <f t="shared" si="36"/>
+        <v>Macros</v>
+      </c>
+      <c r="W26" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X26" s="58" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-GAS-26</v>
+      </c>
+      <c r="Y26" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA26" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB26" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC26" s="64" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4622,32 +4856,52 @@
     <sortCondition ref="F2:F886"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B25">
-    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B24 B25 A25:A26">
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:D1 F1:O1 AB1:AC1 R1:Z1">
-    <cfRule type="cellIs" dxfId="15" priority="56" operator="equal">
+  <conditionalFormatting sqref="A1:D1 F1:O1 R1:Z1 AB1:AC1">
+    <cfRule type="cellIs" dxfId="26" priority="66" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="14" priority="1492"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1502"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10:F1048576 F1:F2">
-    <cfRule type="duplicateValues" dxfId="13" priority="1514"/>
+  <conditionalFormatting sqref="F10:F25 F1:F2 F27:F1048576">
+    <cfRule type="duplicateValues" dxfId="24" priority="1524"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26:F1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1464"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1485"/>
+  <conditionalFormatting sqref="F27:F1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1474"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R25">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q26">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R26">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -4660,15 +4914,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -4733,7 +4987,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -4798,7 +5052,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -4865,7 +5119,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4881,30 +5135,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.61328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="62" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.23046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.07421875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.23046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.61328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.15234375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.23046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -4963,7 +5217,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>1</v>
       </c>
@@ -5022,7 +5276,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>2</v>
       </c>
@@ -5081,7 +5335,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>3</v>
       </c>
@@ -5140,7 +5394,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>4</v>
       </c>
@@ -5202,7 +5456,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="6" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1495"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5212,15 +5466,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -5243,7 +5497,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -5272,22 +5526,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Gases.xlsx
+++ b/Versão5/SIS/Ontologia_Gases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D769D0-CB87-44DC-A1B9-0DE7CE4AC116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560DC78C-777F-4D24-A477-210EB24E17E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1378,7 +1378,121 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="26">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1479,42 +1593,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1540,92 +1618,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2068,15 +2060,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="55" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="55" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="55"/>
+    <col min="1" max="1" width="8.69140625" style="55" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="55" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2087,7 +2079,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2098,7 +2090,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -2109,7 +2101,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2120,7 +2112,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2132,7 +2124,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2144,7 +2136,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2155,7 +2147,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2166,7 +2158,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2177,7 +2169,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2188,7 +2180,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2199,7 +2191,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2210,7 +2202,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2221,7 +2213,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2232,7 +2224,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2243,7 +2235,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2254,7 +2246,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2265,19 +2257,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46260.364439351855</v>
+        <v>46264.570415624999</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2288,7 +2280,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2299,7 +2291,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2310,7 +2302,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2321,7 +2313,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2332,7 +2324,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>86</v>
       </c>
@@ -2353,37 +2345,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="53" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.85546875" style="53" customWidth="1"/>
+    <col min="4" max="4" width="9.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.84375" style="53" customWidth="1"/>
     <col min="12" max="12" width="10" style="53" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="44.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="46.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="40.28515625" style="53" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="55.42578125" style="53" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="40.3046875" style="53" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.84375" style="53" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.15234375" style="53" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="55.3828125" style="53" customWidth="1"/>
+    <col min="26" max="26" width="6.84375" style="53" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="17" style="54" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="53"/>
+    <col min="28" max="28" width="6.84375" style="53" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.15234375" style="53" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="43" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>91</v>
       </c>
@@ -2472,7 +2464,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -2567,7 +2559,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -2662,7 +2654,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -2757,7 +2749,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -2852,7 +2844,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -2947,7 +2939,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -3042,7 +3034,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -3137,7 +3129,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -3232,7 +3224,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -3327,7 +3319,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -3422,7 +3414,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -3517,7 +3509,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -3612,7 +3604,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -3707,7 +3699,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -3802,7 +3794,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -3897,7 +3889,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -3992,7 +3984,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -4087,7 +4079,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="57">
         <v>19</v>
       </c>
@@ -4182,7 +4174,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="57">
         <v>20</v>
       </c>
@@ -4277,7 +4269,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="57">
         <v>21</v>
       </c>
@@ -4372,7 +4364,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="57">
         <v>22</v>
       </c>
@@ -4467,7 +4459,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="57">
         <v>23</v>
       </c>
@@ -4562,7 +4554,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="57">
         <v>24</v>
       </c>
@@ -4657,7 +4649,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="57">
         <v>25</v>
       </c>
@@ -4752,7 +4744,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="57">
         <v>26</v>
       </c>
@@ -4763,10 +4755,10 @@
         <v>247</v>
       </c>
       <c r="D26" s="66" t="s">
+        <v>249</v>
+      </c>
+      <c r="E26" s="66" t="s">
         <v>248</v>
-      </c>
-      <c r="E26" s="66" t="s">
-        <v>249</v>
       </c>
       <c r="F26" s="66" t="s">
         <v>250</v>
@@ -4792,11 +4784,11 @@
       </c>
       <c r="M26" s="33" t="str">
         <f t="shared" si="33"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N26" s="33" t="str">
         <f t="shared" si="33"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O26" s="33" t="str">
         <f t="shared" si="33"/>
@@ -4822,11 +4814,11 @@
       </c>
       <c r="U26" s="30" t="str">
         <f t="shared" si="36"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V26" s="63" t="str">
         <f t="shared" si="36"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W26" s="30" t="s">
         <v>102</v>
@@ -4856,52 +4848,47 @@
     <sortCondition ref="F2:F886"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B24 B25 A25:A26">
-    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+  <conditionalFormatting sqref="A2:B26">
+    <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:D1 F1:O1 R1:Z1 AB1:AC1">
-    <cfRule type="cellIs" dxfId="26" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="66" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="25" priority="1502"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F25 F1:F2 F27:F1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="1524"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1524"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="1474"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1474"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1495"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q26">
+    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R25">
-    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q26">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="R26">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -4914,15 +4901,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -4987,7 +4974,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5052,7 +5039,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5119,7 +5106,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5135,30 +5122,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.53515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="62" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.3046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.3046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.53515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.15234375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -5217,7 +5204,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>1</v>
       </c>
@@ -5276,7 +5263,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>2</v>
       </c>
@@ -5335,7 +5322,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>3</v>
       </c>
@@ -5394,7 +5381,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>4</v>
       </c>
@@ -5456,7 +5443,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="17" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1495"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5466,15 +5453,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -5497,7 +5484,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -5526,22 +5513,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="15" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Gases.xlsx
+++ b/Versão5/SIS/Ontologia_Gases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560DC78C-777F-4D24-A477-210EB24E17E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73880D30-2BD2-4353-B4C3-38336294C68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="272">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -824,10 +824,70 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1358,9 +1418,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1378,7 +1435,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="19">
     <dxf>
       <font>
         <b val="0"/>
@@ -1455,81 +1512,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2060,15 +2047,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="55" customWidth="1"/>
-    <col min="2" max="2" width="40.15234375" style="55" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="55"/>
+    <col min="1" max="1" width="8.7109375" style="55" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="55" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2079,7 +2066,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2090,7 +2077,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -2101,7 +2088,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2112,7 +2099,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2124,7 +2111,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2136,7 +2123,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2147,7 +2134,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2158,7 +2145,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2169,7 +2156,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2180,7 +2167,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2191,7 +2178,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2202,7 +2189,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2213,7 +2200,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2224,7 +2211,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2235,7 +2222,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2246,7 +2233,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2257,19 +2244,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46264.570415624999</v>
+        <v>46268.700799537037</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2280,7 +2267,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2291,7 +2278,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2302,7 +2289,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2313,7 +2300,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2324,7 +2311,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>86</v>
       </c>
@@ -2344,38 +2331,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC26"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD30"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="53" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="53" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.69140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.53515625" style="53" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.84375" style="53" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.85546875" style="53" customWidth="1"/>
     <col min="12" max="12" width="10" style="53" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.69140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.53515625" style="53" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.53515625" style="53" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="44.53515625" style="53" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="46.53515625" style="53" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="40.3046875" style="53" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.53515625" style="53" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.84375" style="53" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.53515625" style="53" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.69140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.15234375" style="53" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="55.3828125" style="53" customWidth="1"/>
-    <col min="26" max="26" width="6.84375" style="53" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="40.28515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="55.42578125" style="53" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="17" style="54" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.84375" style="53" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.15234375" style="53" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="53"/>
+    <col min="28" max="28" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="43" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
         <v>91</v>
       </c>
@@ -2463,8 +2450,11 @@
       <c r="AC1" s="35" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD1" s="35" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -2540,26 +2530,29 @@
         <v>102</v>
       </c>
       <c r="X2" s="58" t="str">
-        <f t="shared" ref="X2:X26" si="5">CONCATENATE("Key-GAS-",A2)</f>
+        <f t="shared" ref="X2:X30" si="5">CONCATENATE("Key-GAS-",A2)</f>
         <v>Key-GAS-2</v>
       </c>
       <c r="Y2" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z2" s="64" t="s">
+      <c r="Z2" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB2" s="64" t="s">
+      <c r="AB2" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD2" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -2641,20 +2634,23 @@
       <c r="Y3" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z3" s="64" t="s">
+      <c r="Z3" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB3" s="64" t="s">
+      <c r="AB3" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD3" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -2736,20 +2732,23 @@
       <c r="Y4" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z4" s="64" t="s">
+      <c r="Z4" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB4" s="64" t="s">
+      <c r="AB4" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD4" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -2831,20 +2830,23 @@
       <c r="Y5" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z5" s="64" t="s">
+      <c r="Z5" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="AB5" s="64" t="s">
+      <c r="AB5" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD5" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -2926,20 +2928,23 @@
       <c r="Y6" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z6" s="64" t="s">
+      <c r="Z6" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB6" s="64" t="s">
+      <c r="AB6" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD6" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -3021,20 +3026,23 @@
       <c r="Y7" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z7" s="64" t="s">
+      <c r="Z7" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA7" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB7" s="64" t="s">
+      <c r="AB7" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD7" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -3116,20 +3124,23 @@
       <c r="Y8" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z8" s="64" t="s">
+      <c r="Z8" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB8" s="64" t="s">
+      <c r="AB8" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD8" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -3211,20 +3222,23 @@
       <c r="Y9" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="Z9" s="64" t="s">
+      <c r="Z9" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA9" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="AB9" s="64" t="s">
+      <c r="AB9" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD9" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -3306,20 +3320,23 @@
       <c r="Y10" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z10" s="64" t="s">
+      <c r="Z10" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="AB10" s="64" t="s">
+      <c r="AB10" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD10" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -3401,20 +3418,23 @@
       <c r="Y11" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z11" s="64" t="s">
+      <c r="Z11" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="AB11" s="64" t="s">
+      <c r="AB11" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD11" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -3496,20 +3516,23 @@
       <c r="Y12" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z12" s="64" t="s">
+      <c r="Z12" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="AB12" s="64" t="s">
+      <c r="AB12" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD12" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -3591,20 +3614,23 @@
       <c r="Y13" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z13" s="64" t="s">
+      <c r="Z13" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="AB13" s="64" t="s">
+      <c r="AB13" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD13" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -3686,20 +3712,23 @@
       <c r="Y14" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="Z14" s="64" t="s">
+      <c r="Z14" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="AB14" s="64" t="s">
+      <c r="AB14" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD14" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -3781,20 +3810,23 @@
       <c r="Y15" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="Z15" s="64" t="s">
+      <c r="Z15" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB15" s="64" t="s">
+      <c r="AB15" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD15" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -3876,20 +3908,23 @@
       <c r="Y16" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="Z16" s="64" t="s">
+      <c r="Z16" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB16" s="64" t="s">
+      <c r="AB16" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD16" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -3971,20 +4006,23 @@
       <c r="Y17" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="Z17" s="64" t="s">
+      <c r="Z17" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB17" s="64" t="s">
+      <c r="AB17" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD17" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -4066,20 +4104,23 @@
       <c r="Y18" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z18" s="64" t="s">
+      <c r="Z18" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB18" s="64" t="s">
+      <c r="AB18" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD18" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="57">
         <v>19</v>
       </c>
@@ -4161,20 +4202,23 @@
       <c r="Y19" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z19" s="64" t="s">
+      <c r="Z19" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB19" s="64" t="s">
+      <c r="AB19" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD19" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="57">
         <v>20</v>
       </c>
@@ -4256,20 +4300,23 @@
       <c r="Y20" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z20" s="64" t="s">
+      <c r="Z20" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="AB20" s="64" t="s">
+      <c r="AB20" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD20" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="57">
         <v>21</v>
       </c>
@@ -4351,20 +4398,23 @@
       <c r="Y21" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="Z21" s="64" t="s">
+      <c r="Z21" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA21" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="AB21" s="64" t="s">
+      <c r="AB21" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC21" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD21" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="57">
         <v>22</v>
       </c>
@@ -4446,20 +4496,23 @@
       <c r="Y22" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z22" s="64" t="s">
+      <c r="Z22" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA22" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB22" s="64" t="s">
+      <c r="AB22" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC22" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD22" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="57">
         <v>23</v>
       </c>
@@ -4541,20 +4594,23 @@
       <c r="Y23" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z23" s="64" t="s">
+      <c r="Z23" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA23" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB23" s="64" t="s">
+      <c r="AB23" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC23" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD23" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="57">
         <v>24</v>
       </c>
@@ -4636,20 +4692,23 @@
       <c r="Y24" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Z24" s="64" t="s">
+      <c r="Z24" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="AB24" s="64" t="s">
+      <c r="AB24" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC24" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD24" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="57">
         <v>25</v>
       </c>
@@ -4731,36 +4790,39 @@
       <c r="Y25" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="Z25" s="64" t="s">
+      <c r="Z25" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="AB25" s="64" t="s">
+      <c r="AB25" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC25" s="30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="26" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD25" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="57">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C26" s="65" t="s">
         <v>247</v>
       </c>
-      <c r="D26" s="66" t="s">
+      <c r="D26" s="65" t="s">
         <v>249</v>
       </c>
-      <c r="E26" s="66" t="s">
+      <c r="E26" s="65" t="s">
         <v>248</v>
       </c>
-      <c r="F26" s="66" t="s">
+      <c r="F26" s="65" t="s">
         <v>250</v>
       </c>
       <c r="G26" s="60" t="s">
@@ -4779,7 +4841,7 @@
         <v>9</v>
       </c>
       <c r="L26" s="33" t="str">
-        <f t="shared" ref="L26:O26" si="33">SUBSTITUTE(CONCATENATE("", C26), ".", " ")</f>
+        <f t="shared" ref="L26:O30" si="33">SUBSTITUTE(CONCATENATE("", C26), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M26" s="33" t="str">
@@ -4792,32 +4854,30 @@
       </c>
       <c r="O26" s="33" t="str">
         <f t="shared" si="33"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P26" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="Q26" s="62" t="str">
-        <f t="shared" ref="Q26" si="34">_xlfn.TRANSLATE(P26,"pt","es")</f>
-        <v>Aplicación Revit</v>
-      </c>
-      <c r="R26" s="62" t="str">
-        <f t="shared" ref="R26" si="35">_xlfn.TRANSLATE(P26,"pt","en")</f>
-        <v>Revit App</v>
+      <c r="Q26" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="R26" s="30" t="s">
+        <v>253</v>
       </c>
       <c r="S26" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T26" s="30" t="str">
-        <f t="shared" ref="T26:V26" si="36">SUBSTITUTE(C26, ".", " ")</f>
+        <f t="shared" ref="T26:V30" si="34">SUBSTITUTE(C26, ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="U26" s="30" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>Macros</v>
       </c>
-      <c r="V26" s="63" t="str">
-        <f t="shared" si="36"/>
+      <c r="V26" s="62" t="str">
+        <f t="shared" si="34"/>
         <v>Métodos</v>
       </c>
       <c r="W26" s="30" t="s">
@@ -4827,19 +4887,422 @@
         <f t="shared" si="5"/>
         <v>Key-GAS-26</v>
       </c>
-      <c r="Y26" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z26" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA26" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB26" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC26" s="64" t="s">
+      <c r="Y26" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA26" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB26" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC26" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD26" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="57">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C27" s="65" t="s">
+        <v>247</v>
+      </c>
+      <c r="D27" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="E27" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="F27" s="65" t="s">
+        <v>254</v>
+      </c>
+      <c r="G27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>De API</v>
+      </c>
+      <c r="M27" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Macros</v>
+      </c>
+      <c r="N27" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O27" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P27" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q27" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="R27" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="S27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T27" s="30" t="str">
+        <f t="shared" si="34"/>
+        <v>De API</v>
+      </c>
+      <c r="U27" s="30" t="str">
+        <f t="shared" si="34"/>
+        <v>Macros</v>
+      </c>
+      <c r="V27" s="62" t="str">
+        <f t="shared" si="34"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W27" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X27" s="58" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-GAS-27</v>
+      </c>
+      <c r="Y27" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z27" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA27" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB27" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC27" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD27" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="57">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C28" s="65" t="s">
+        <v>247</v>
+      </c>
+      <c r="D28" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="E28" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="F28" s="65" t="s">
+        <v>258</v>
+      </c>
+      <c r="G28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>De API</v>
+      </c>
+      <c r="M28" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Macros</v>
+      </c>
+      <c r="N28" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O28" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P28" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q28" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="R28" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="S28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T28" s="30" t="str">
+        <f t="shared" si="34"/>
+        <v>De API</v>
+      </c>
+      <c r="U28" s="30" t="str">
+        <f t="shared" si="34"/>
+        <v>Macros</v>
+      </c>
+      <c r="V28" s="62" t="str">
+        <f t="shared" si="34"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W28" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X28" s="58" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-GAS-28</v>
+      </c>
+      <c r="Y28" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z28" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB28" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD28" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="57">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C29" s="65" t="s">
+        <v>247</v>
+      </c>
+      <c r="D29" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="E29" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="F29" s="65" t="s">
+        <v>262</v>
+      </c>
+      <c r="G29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L29" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>De API</v>
+      </c>
+      <c r="M29" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Macros</v>
+      </c>
+      <c r="N29" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O29" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P29" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q29" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="R29" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="S29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T29" s="30" t="str">
+        <f t="shared" si="34"/>
+        <v>De API</v>
+      </c>
+      <c r="U29" s="30" t="str">
+        <f t="shared" si="34"/>
+        <v>Macros</v>
+      </c>
+      <c r="V29" s="62" t="str">
+        <f t="shared" si="34"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W29" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X29" s="58" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-GAS-29</v>
+      </c>
+      <c r="Y29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD29" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="57">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" s="65" t="s">
+        <v>247</v>
+      </c>
+      <c r="D30" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" s="65" t="s">
+        <v>266</v>
+      </c>
+      <c r="F30" s="65" t="s">
+        <v>267</v>
+      </c>
+      <c r="G30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L30" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>De API</v>
+      </c>
+      <c r="M30" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Macros</v>
+      </c>
+      <c r="N30" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O30" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P30" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q30" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="R30" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="S30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T30" s="30" t="str">
+        <f t="shared" si="34"/>
+        <v>De API</v>
+      </c>
+      <c r="U30" s="30" t="str">
+        <f t="shared" si="34"/>
+        <v>Macros</v>
+      </c>
+      <c r="V30" s="62" t="str">
+        <f t="shared" si="34"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W30" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X30" s="58" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-GAS-30</v>
+      </c>
+      <c r="Y30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD30" s="63" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4848,47 +5311,38 @@
     <sortCondition ref="F2:F886"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B26">
-    <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
+  <conditionalFormatting sqref="A2:B30">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:D1 F1:O1 R1:Z1 AB1:AC1">
-    <cfRule type="cellIs" dxfId="24" priority="66" operator="equal">
+  <conditionalFormatting sqref="A1:D1 F1:O1 R1:Z1 AB1:AD1">
+    <cfRule type="cellIs" dxfId="17" priority="70" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E30:F30">
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="23" priority="1502"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1506"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10:F25 F1:F2 F27:F1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="1524"/>
+  <conditionalFormatting sqref="F10:F25 F1:F2 F31:F1048576">
+    <cfRule type="duplicateValues" dxfId="14" priority="1528"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
+  <conditionalFormatting sqref="F26:F29">
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27:F1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1474"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1495"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q26">
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
+  <conditionalFormatting sqref="F31:F1048576">
+    <cfRule type="duplicateValues" dxfId="12" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1478"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R25">
-    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R26">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -4901,15 +5355,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -4974,7 +5428,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5039,7 +5493,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5122,30 +5576,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.15234375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="62" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.15234375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -5204,7 +5658,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>1</v>
       </c>
@@ -5263,7 +5717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>2</v>
       </c>
@@ -5322,7 +5776,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>3</v>
       </c>
@@ -5381,7 +5835,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>4</v>
       </c>
@@ -5453,15 +5907,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -5484,7 +5938,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>

--- a/Versão5/SIS/Ontologia_Gases.xlsx
+++ b/Versão5/SIS/Ontologia_Gases.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73880D30-2BD2-4353-B4C3-38336294C68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDA9F70-BA8E-4079-9CB6-5AEE87190316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
     <sheet name="Classes" sheetId="17" r:id="rId2"/>
-    <sheet name="Disjunt" sheetId="3" r:id="rId3"/>
-    <sheet name="FatosIn" sheetId="25" r:id="rId4"/>
-    <sheet name="Interop" sheetId="16" r:id="rId5"/>
+    <sheet name="Planilha1" sheetId="26" r:id="rId3"/>
+    <sheet name="Disjunt" sheetId="3" r:id="rId4"/>
+    <sheet name="FatosIn" sheetId="25" r:id="rId5"/>
+    <sheet name="Interop" sheetId="16" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classes!#REF!</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="293">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -888,6 +889,69 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>De.Materialidade</t>
+  </si>
+  <si>
+    <t>Materialidades</t>
+  </si>
+  <si>
+    <t>Materiais</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_PipeMaterials ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.Cobre</t>
+  </si>
+  <si>
+    <t>Copper pipe for hot water or gas networks.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20.05 ]</t>
+  </si>
+  <si>
+    <t>[ 0M.20.60.07.09 ]</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20.01.01 ]</t>
+  </si>
+  <si>
+    <t>Tubo de cobre para redes de água e gás.</t>
+  </si>
+  <si>
+    <t>Tubería de cobre para redes de agua y gas.</t>
+  </si>
+  <si>
+    <t>Tubo.Multicamada</t>
+  </si>
+  <si>
+    <t>Tubo composto por uma camada interna de plástico (PEX), uma camada intermediária de alumínio contínuo (Al) e uma camada externa de plástico protetor. Tubo flexível conectado por crimpagem.</t>
+  </si>
+  <si>
+    <t>Tubo compuesto por una capa interior de plástico (PEX), una capa intermedia de aluminio continuo (Al) y una capa exterior de plástico protector. Tubo flexible conectado mediante crimping.</t>
+  </si>
+  <si>
+    <t>Tube composed of an inner layer of plastic (PEX), a middle layer of continuous aluminium (Al) and an outer layer of protective plastic. Flexible tube connected by crimping.</t>
+  </si>
+  <si>
+    <t>Tubo de aço com costura (especificações NBR 5580 ou NBR 5590).</t>
+  </si>
+  <si>
+    <t>Tubería de acero soldada (especificaciones NBR 5580 o NBR 5590).</t>
+  </si>
+  <si>
+    <t>Welded steel pipe (NBR 5580 or NBR 5590 specifications).</t>
+  </si>
+  <si>
+    <t>Tubo.de.Aço.Costura</t>
+  </si>
+  <si>
+    <t>c</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1431,11 +1495,138 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1509,6 +1700,56 @@
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2047,15 +2288,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="55" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="55" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="55"/>
+    <col min="1" max="1" width="8.69140625" style="55" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="55" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2066,7 +2307,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2077,7 +2318,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -2088,7 +2329,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2099,7 +2340,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2111,7 +2352,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2123,7 +2364,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2134,7 +2375,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2145,7 +2386,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2156,7 +2397,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2167,7 +2408,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2178,7 +2419,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2189,7 +2430,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2200,7 +2441,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2211,7 +2452,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2222,7 +2463,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2233,7 +2474,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2244,19 +2485,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46268.700799537037</v>
+        <v>46270.453988657406</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2267,7 +2508,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2278,7 +2519,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2289,7 +2530,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2300,7 +2541,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2311,7 +2552,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>86</v>
       </c>
@@ -2331,38 +2572,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AD30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AD33"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="53" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.85546875" style="53" customWidth="1"/>
+    <col min="4" max="4" width="9.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.84375" style="53" customWidth="1"/>
     <col min="12" max="12" width="10" style="53" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="44.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="46.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="40.28515625" style="53" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="55.42578125" style="53" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="40.3046875" style="53" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.84375" style="53" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.53515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.15234375" style="53" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="55.3828125" style="53" customWidth="1"/>
+    <col min="26" max="26" width="6.84375" style="53" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="17" style="54" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="53"/>
+    <col min="28" max="28" width="6.84375" style="53" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.3828125" style="53" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="43" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>91</v>
       </c>
@@ -2454,24 +2695,24 @@
         <v>271</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="57">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C2" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>158</v>
+      <c r="C2" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>291</v>
       </c>
       <c r="G2" s="60" t="s">
         <v>9</v>
@@ -2489,87 +2730,89 @@
         <v>9</v>
       </c>
       <c r="L2" s="33" t="str">
-        <f t="shared" ref="L2:L20" si="0">CONCATENATE("", C2)</f>
-        <v>Sistemas.Prediais</v>
+        <f>SUBSTITUTE(CONCATENATE("", C2), ".", " ")</f>
+        <v>De Materialidade</v>
       </c>
       <c r="M2" s="33" t="str">
-        <f t="shared" ref="M2:M20" si="1">CONCATENATE("", D2)</f>
-        <v>Sistema.Gases</v>
+        <f>SUBSTITUTE(CONCATENATE("", D2), ".", " ")</f>
+        <v>Materialidades</v>
       </c>
       <c r="N2" s="33" t="str">
-        <f t="shared" ref="N2:N20" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Sistema de Gás</v>
-      </c>
-      <c r="O2" s="30" t="str">
-        <f t="shared" ref="O2:O9" si="3">IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),CONCATENATE("",F2))</f>
-        <v>Sistema.GAS</v>
-      </c>
-      <c r="P2" s="52" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q2" s="52" t="s">
-        <v>139</v>
+        <f>SUBSTITUTE(CONCATENATE("", E2), ".", " ")</f>
+        <v>Materiais</v>
+      </c>
+      <c r="O2" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", F2), ".", " ")</f>
+        <v>Tubo de Aço Costura</v>
+      </c>
+      <c r="P2" s="66" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>289</v>
       </c>
       <c r="R2" s="30" t="s">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="S2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="U2" s="30" t="s">
-        <v>101</v>
+      <c r="T2" s="30" t="str">
+        <f>SUBSTITUTE(C2, ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U2" s="30" t="str">
+        <f>SUBSTITUTE(D2, ".", " ")</f>
+        <v>Materialidades</v>
       </c>
       <c r="V2" s="30" t="str">
-        <f t="shared" ref="V2:V20" si="4">SUBSTITUTE(E2, "_", " ")</f>
-        <v>Sistema.de.Gás</v>
+        <f>SUBSTITUTE(E2, ".", " ")</f>
+        <v>Materiais</v>
       </c>
       <c r="W2" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X2" s="58" t="str">
-        <f t="shared" ref="X2:X30" si="5">CONCATENATE("Key-GAS-",A2)</f>
+        <f t="shared" ref="X2:X4" si="0">CONCATENATE("Key-GAS-",A2)</f>
         <v>Key-GAS-2</v>
       </c>
-      <c r="Y2" s="29" t="s">
-        <v>108</v>
+      <c r="Y2" s="30" t="s">
+        <v>275</v>
       </c>
       <c r="Z2" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="29" t="s">
-        <v>179</v>
+      <c r="AA2" s="30" t="s">
+        <v>276</v>
       </c>
       <c r="AB2" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="AD2" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="57">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C3" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>165</v>
+      <c r="C3" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="F3" s="56" t="s">
-        <v>159</v>
+        <v>277</v>
       </c>
       <c r="G3" s="60" t="s">
         <v>9</v>
@@ -2587,87 +2830,89 @@
         <v>9</v>
       </c>
       <c r="L3" s="33" t="str">
-        <f t="shared" ref="L3:L14" si="6">CONCATENATE("", C3)</f>
-        <v>Sistemas.Prediais</v>
+        <f>SUBSTITUTE(CONCATENATE("", C3), ".", " ")</f>
+        <v>De Materialidade</v>
       </c>
       <c r="M3" s="33" t="str">
-        <f t="shared" ref="M3:M14" si="7">CONCATENATE("", D3)</f>
-        <v>Sistema.Gases</v>
+        <f>SUBSTITUTE(CONCATENATE("", D3), ".", " ")</f>
+        <v>Materialidades</v>
       </c>
       <c r="N3" s="33" t="str">
-        <f t="shared" ref="N3:N14" si="8">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
-        <v>Sistema de Gás Hospitalar</v>
-      </c>
-      <c r="O3" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Oxigênio</v>
-      </c>
-      <c r="P3" s="52" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q3" s="52" t="s">
-        <v>172</v>
+        <f>SUBSTITUTE(CONCATENATE("", E3), ".", " ")</f>
+        <v>Materiais</v>
+      </c>
+      <c r="O3" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", F3), ".", " ")</f>
+        <v>Tubo de Cobre</v>
+      </c>
+      <c r="P3" s="66" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>283</v>
       </c>
       <c r="R3" s="30" t="s">
-        <v>203</v>
+        <v>278</v>
       </c>
       <c r="S3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="U3" s="30" t="s">
-        <v>101</v>
+      <c r="T3" s="30" t="str">
+        <f>SUBSTITUTE(C3, ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U3" s="30" t="str">
+        <f>SUBSTITUTE(D3, ".", " ")</f>
+        <v>Materialidades</v>
       </c>
       <c r="V3" s="30" t="str">
-        <f t="shared" ref="V3:V14" si="9">SUBSTITUTE(E3, "_", " ")</f>
-        <v>Sistema.de.Gás.Hospitalar</v>
+        <f>SUBSTITUTE(E3, ".", " ")</f>
+        <v>Materiais</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X3" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Key-GAS-3</v>
       </c>
-      <c r="Y3" s="29" t="s">
-        <v>108</v>
+      <c r="Y3" s="30" t="s">
+        <v>275</v>
       </c>
       <c r="Z3" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="AA3" s="29" t="s">
-        <v>179</v>
+      <c r="AA3" s="30" t="s">
+        <v>276</v>
       </c>
       <c r="AB3" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="AD3" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="57">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C4" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>165</v>
+      <c r="C4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>160</v>
+        <v>284</v>
       </c>
       <c r="G4" s="60" t="s">
         <v>9</v>
@@ -2685,70 +2930,72 @@
         <v>9</v>
       </c>
       <c r="L4" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
+        <f>SUBSTITUTE(CONCATENATE("", C4), ".", " ")</f>
+        <v>De Materialidade</v>
       </c>
       <c r="M4" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistema.Gases</v>
+        <f>SUBSTITUTE(CONCATENATE("", D4), ".", " ")</f>
+        <v>Materialidades</v>
       </c>
       <c r="N4" s="33" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistema de Gás Hospitalar</v>
-      </c>
-      <c r="O4" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Ar.Medicinal</v>
-      </c>
-      <c r="P4" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q4" s="52" t="s">
-        <v>173</v>
+        <f>SUBSTITUTE(CONCATENATE("", E4), ".", " ")</f>
+        <v>Materiais</v>
+      </c>
+      <c r="O4" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", F4), ".", " ")</f>
+        <v>Tubo Multicamada</v>
+      </c>
+      <c r="P4" s="66" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>286</v>
       </c>
       <c r="R4" s="30" t="s">
-        <v>204</v>
+        <v>287</v>
       </c>
       <c r="S4" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="U4" s="30" t="s">
-        <v>101</v>
+      <c r="T4" s="30" t="str">
+        <f>SUBSTITUTE(C4, ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U4" s="30" t="str">
+        <f>SUBSTITUTE(D4, ".", " ")</f>
+        <v>Materialidades</v>
       </c>
       <c r="V4" s="30" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
+        <f>SUBSTITUTE(E4, ".", " ")</f>
+        <v>Materiais</v>
       </c>
       <c r="W4" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X4" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Key-GAS-4</v>
       </c>
-      <c r="Y4" s="29" t="s">
-        <v>108</v>
+      <c r="Y4" s="30" t="s">
+        <v>275</v>
       </c>
       <c r="Z4" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" s="29" t="s">
-        <v>179</v>
+      <c r="AA4" s="30" t="s">
+        <v>276</v>
       </c>
       <c r="AB4" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="AD4" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -2762,10 +3009,10 @@
         <v>115</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="F5" s="56" t="s">
-        <v>161</v>
+        <v>116</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>158</v>
       </c>
       <c r="G5" s="60" t="s">
         <v>9</v>
@@ -2783,29 +3030,29 @@
         <v>9</v>
       </c>
       <c r="L5" s="33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L5:L23" si="1">CONCATENATE("", C5)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M5" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="M5:M23" si="2">CONCATENATE("", D5)</f>
         <v>Sistema.Gases</v>
       </c>
       <c r="N5" s="33" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistema de Gás Hospitalar</v>
+        <f t="shared" ref="N5:N23" si="3">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E5),"."," ")," De "," de "))</f>
+        <v>Sistema de Gás</v>
       </c>
       <c r="O5" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Ar.Comprimido</v>
+        <f t="shared" ref="O5:O12" si="4">IF(ISNUMBER(FIND("Ifc",F5)),CONCATENATE("Classe IFC:   ",F5),CONCATENATE("",F5))</f>
+        <v>Sistema.GAS</v>
       </c>
       <c r="P5" s="52" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="Q5" s="52" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="R5" s="30" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="S5" s="30" t="s">
         <v>9</v>
@@ -2817,14 +3064,14 @@
         <v>101</v>
       </c>
       <c r="V5" s="30" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
+        <f t="shared" ref="V5:V23" si="5">SUBSTITUTE(E5, "_", " ")</f>
+        <v>Sistema.de.Gás</v>
       </c>
       <c r="W5" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X5" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="X5:X33" si="6">CONCATENATE("Key-GAS-",A5)</f>
         <v>Key-GAS-5</v>
       </c>
       <c r="Y5" s="29" t="s">
@@ -2834,19 +3081,19 @@
         <v>9</v>
       </c>
       <c r="AA5" s="29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AB5" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AD5" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -2863,7 +3110,7 @@
         <v>165</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G6" s="60" t="s">
         <v>9</v>
@@ -2881,29 +3128,29 @@
         <v>9</v>
       </c>
       <c r="L6" s="33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L6:L17" si="7">CONCATENATE("", C6)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M6" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="M6:M17" si="8">CONCATENATE("", D6)</f>
         <v>Sistema.Gases</v>
       </c>
       <c r="N6" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="N6:N17" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O6" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Óxido.Nitroso</v>
+        <f t="shared" si="4"/>
+        <v>Sistema.Oxigênio</v>
       </c>
       <c r="P6" s="52" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q6" s="52" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="R6" s="30" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="S6" s="30" t="s">
         <v>9</v>
@@ -2915,14 +3162,14 @@
         <v>101</v>
       </c>
       <c r="V6" s="30" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="V6:V17" si="10">SUBSTITUTE(E6, "_", " ")</f>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W6" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-6</v>
       </c>
       <c r="Y6" s="29" t="s">
@@ -2944,7 +3191,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -2961,7 +3208,7 @@
         <v>165</v>
       </c>
       <c r="F7" s="56" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G7" s="60" t="s">
         <v>9</v>
@@ -2979,29 +3226,29 @@
         <v>9</v>
       </c>
       <c r="L7" s="33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M7" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Sistema.Gases</v>
       </c>
       <c r="N7" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O7" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Nitrogênio</v>
+        <f t="shared" si="4"/>
+        <v>Sistema.Ar.Medicinal</v>
       </c>
       <c r="P7" s="52" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q7" s="52" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="R7" s="30" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="S7" s="30" t="s">
         <v>9</v>
@@ -3013,14 +3260,14 @@
         <v>101</v>
       </c>
       <c r="V7" s="30" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W7" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X7" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-7</v>
       </c>
       <c r="Y7" s="29" t="s">
@@ -3042,7 +3289,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -3059,7 +3306,7 @@
         <v>165</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G8" s="60" t="s">
         <v>9</v>
@@ -3077,29 +3324,29 @@
         <v>9</v>
       </c>
       <c r="L8" s="33" t="str">
-        <f t="shared" ref="L8" si="10">CONCATENATE("", C8)</f>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M8" s="33" t="str">
-        <f t="shared" ref="M8" si="11">CONCATENATE("", D8)</f>
+        <f t="shared" si="8"/>
         <v>Sistema.Gases</v>
       </c>
       <c r="N8" s="33" t="str">
-        <f t="shared" ref="N8" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
+        <f t="shared" si="9"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O8" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Hélio</v>
+        <f t="shared" si="4"/>
+        <v>Sistema.Ar.Comprimido</v>
       </c>
       <c r="P8" s="52" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q8" s="52" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="R8" s="30" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="S8" s="30" t="s">
         <v>9</v>
@@ -3111,14 +3358,14 @@
         <v>101</v>
       </c>
       <c r="V8" s="30" t="str">
-        <f t="shared" ref="V8" si="13">SUBSTITUTE(E8, "_", " ")</f>
+        <f t="shared" si="10"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W8" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X8" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-8</v>
       </c>
       <c r="Y8" s="29" t="s">
@@ -3128,7 +3375,7 @@
         <v>9</v>
       </c>
       <c r="AA8" s="29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB8" s="63" t="s">
         <v>9</v>
@@ -3140,7 +3387,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -3157,7 +3404,7 @@
         <v>165</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="G9" s="60" t="s">
         <v>9</v>
@@ -3175,29 +3422,29 @@
         <v>9</v>
       </c>
       <c r="L9" s="33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M9" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Sistema.Gases</v>
       </c>
       <c r="N9" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O9" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Vacuo</v>
+        <f t="shared" si="4"/>
+        <v>Sistema.Óxido.Nitroso</v>
       </c>
       <c r="P9" s="52" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="Q9" s="52" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="S9" s="30" t="s">
         <v>9</v>
@@ -3209,14 +3456,14 @@
         <v>101</v>
       </c>
       <c r="V9" s="30" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W9" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X9" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-9</v>
       </c>
       <c r="Y9" s="29" t="s">
@@ -3226,7 +3473,7 @@
         <v>9</v>
       </c>
       <c r="AA9" s="29" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AB9" s="63" t="s">
         <v>9</v>
@@ -3238,7 +3485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -3248,14 +3495,14 @@
       <c r="C10" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>227</v>
+      <c r="D10" s="42" t="s">
+        <v>115</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="F10" s="42" t="s">
-        <v>125</v>
+        <v>165</v>
+      </c>
+      <c r="F10" s="56" t="s">
+        <v>163</v>
       </c>
       <c r="G10" s="60" t="s">
         <v>9</v>
@@ -3273,29 +3520,29 @@
         <v>9</v>
       </c>
       <c r="L10" s="33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M10" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.Gases</v>
+        <f t="shared" si="8"/>
+        <v>Sistema.Gases</v>
       </c>
       <c r="N10" s="33" t="str">
-        <f t="shared" si="8"/>
-        <v>Peças Gás</v>
+        <f t="shared" si="9"/>
+        <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O10" s="30" t="str">
-        <f>IF(ISNUMBER(FIND("Ifc",F10)),CONCATENATE("Classe IFC:   ",F10),CONCATENATE("",F10))</f>
-        <v>Queimador</v>
+        <f t="shared" si="4"/>
+        <v>Sistema.Nitrogênio</v>
       </c>
       <c r="P10" s="52" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="Q10" s="52" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="R10" s="30" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="S10" s="30" t="s">
         <v>9</v>
@@ -3307,36 +3554,36 @@
         <v>101</v>
       </c>
       <c r="V10" s="30" t="str">
-        <f t="shared" si="9"/>
-        <v>Peças.Gás</v>
+        <f t="shared" si="10"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W10" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X10" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-10</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="Z10" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="29" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="AB10" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AD10" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -3346,14 +3593,14 @@
       <c r="C11" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>227</v>
+      <c r="D11" s="42" t="s">
+        <v>115</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>157</v>
+        <v>165</v>
+      </c>
+      <c r="F11" s="56" t="s">
+        <v>164</v>
       </c>
       <c r="G11" s="60" t="s">
         <v>9</v>
@@ -3371,29 +3618,29 @@
         <v>9</v>
       </c>
       <c r="L11" s="33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L11" si="11">CONCATENATE("", C11)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M11" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.Gases</v>
+        <f t="shared" ref="M11" si="12">CONCATENATE("", D11)</f>
+        <v>Sistema.Gases</v>
       </c>
       <c r="N11" s="33" t="str">
-        <f t="shared" si="8"/>
-        <v>Peças Gás</v>
+        <f t="shared" ref="N11" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
+        <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O11" s="30" t="str">
-        <f t="shared" ref="O11:O24" si="14">IF(ISNUMBER(FIND("Ifc",F11)),CONCATENATE("Classe IFC:   ",F11),CONCATENATE("",F11))</f>
-        <v>Registro.de.Gás</v>
+        <f t="shared" si="4"/>
+        <v>Sistema.Hélio</v>
       </c>
       <c r="P11" s="52" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="Q11" s="52" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="R11" s="30" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="S11" s="30" t="s">
         <v>9</v>
@@ -3405,36 +3652,36 @@
         <v>101</v>
       </c>
       <c r="V11" s="30" t="str">
-        <f t="shared" si="9"/>
-        <v>Peças.Gás</v>
+        <f t="shared" ref="V11" si="14">SUBSTITUTE(E11, "_", " ")</f>
+        <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X11" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-11</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="Z11" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="29" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="AB11" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AD11" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -3444,14 +3691,14 @@
       <c r="C12" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>227</v>
+      <c r="D12" s="42" t="s">
+        <v>115</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="F12" s="42" t="s">
-        <v>156</v>
+        <v>165</v>
+      </c>
+      <c r="F12" s="56" t="s">
+        <v>180</v>
       </c>
       <c r="G12" s="60" t="s">
         <v>9</v>
@@ -3469,29 +3716,29 @@
         <v>9</v>
       </c>
       <c r="L12" s="33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M12" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.Gases</v>
+        <f t="shared" si="8"/>
+        <v>Sistema.Gases</v>
       </c>
       <c r="N12" s="33" t="str">
-        <f t="shared" si="8"/>
-        <v>Peças Gás</v>
+        <f t="shared" si="9"/>
+        <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O12" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Válvula.de.Gás</v>
+        <f t="shared" si="4"/>
+        <v>Sistema.Vacuo</v>
       </c>
       <c r="P12" s="52" t="s">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="Q12" s="52" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="R12" s="30" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="S12" s="30" t="s">
         <v>9</v>
@@ -3503,36 +3750,36 @@
         <v>101</v>
       </c>
       <c r="V12" s="30" t="str">
-        <f t="shared" si="9"/>
-        <v>Peças.Gás</v>
+        <f t="shared" si="10"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W12" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X12" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-12</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="Z12" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="29" t="s">
-        <v>103</v>
+        <v>182</v>
       </c>
       <c r="AB12" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AD12" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -3549,7 +3796,7 @@
         <v>117</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="G13" s="60" t="s">
         <v>9</v>
@@ -3567,29 +3814,29 @@
         <v>9</v>
       </c>
       <c r="L13" s="33" t="str">
-        <f t="shared" ref="L13" si="15">CONCATENATE("", C13)</f>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M13" s="33" t="str">
-        <f t="shared" ref="M13" si="16">CONCATENATE("", D13)</f>
+        <f t="shared" si="8"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N13" s="33" t="str">
-        <f t="shared" ref="N13" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
+        <f t="shared" si="9"/>
         <v>Peças Gás</v>
       </c>
       <c r="O13" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Medidor.de.Gás</v>
+        <f>IF(ISNUMBER(FIND("Ifc",F13)),CONCATENATE("Classe IFC:   ",F13),CONCATENATE("",F13))</f>
+        <v>Queimador</v>
       </c>
       <c r="P13" s="52" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q13" s="52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R13" s="30" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="S13" s="30" t="s">
         <v>9</v>
@@ -3601,14 +3848,14 @@
         <v>101</v>
       </c>
       <c r="V13" s="30" t="str">
-        <f t="shared" ref="V13" si="18">SUBSTITUTE(E13, "_", " ")</f>
+        <f t="shared" si="10"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W13" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X13" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-13</v>
       </c>
       <c r="Y13" s="29" t="s">
@@ -3618,7 +3865,7 @@
         <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="AB13" s="63" t="s">
         <v>9</v>
@@ -3630,7 +3877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -3647,7 +3894,7 @@
         <v>117</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>223</v>
+        <v>157</v>
       </c>
       <c r="G14" s="60" t="s">
         <v>9</v>
@@ -3665,29 +3912,29 @@
         <v>9</v>
       </c>
       <c r="L14" s="33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M14" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N14" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Peças Gás</v>
       </c>
       <c r="O14" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Acessório.de.Gás</v>
+        <f t="shared" ref="O14:O27" si="15">IF(ISNUMBER(FIND("Ifc",F14)),CONCATENATE("Classe IFC:   ",F14),CONCATENATE("",F14))</f>
+        <v>Registro.de.Gás</v>
       </c>
       <c r="P14" s="52" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q14" s="52" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R14" s="30" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="S14" s="30" t="s">
         <v>9</v>
@@ -3699,24 +3946,24 @@
         <v>101</v>
       </c>
       <c r="V14" s="30" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W14" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X14" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-14</v>
       </c>
       <c r="Y14" s="29" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="Z14" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="AB14" s="63" t="s">
         <v>9</v>
@@ -3728,7 +3975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -3745,7 +3992,7 @@
         <v>117</v>
       </c>
       <c r="F15" s="42" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="G15" s="60" t="s">
         <v>9</v>
@@ -3763,29 +4010,29 @@
         <v>9</v>
       </c>
       <c r="L15" s="33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M15" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N15" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>Peças Gás</v>
       </c>
       <c r="O15" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Buchão.de.Gás</v>
+        <f t="shared" si="15"/>
+        <v>Válvula.de.Gás</v>
       </c>
       <c r="P15" s="52" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="Q15" s="52" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="R15" s="30" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="S15" s="30" t="s">
         <v>9</v>
@@ -3797,24 +4044,24 @@
         <v>101</v>
       </c>
       <c r="V15" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W15" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X15" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-15</v>
       </c>
       <c r="Y15" s="29" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="Z15" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AB15" s="63" t="s">
         <v>9</v>
@@ -3826,7 +4073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -3843,7 +4090,7 @@
         <v>117</v>
       </c>
       <c r="F16" s="42" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="G16" s="60" t="s">
         <v>9</v>
@@ -3861,29 +4108,29 @@
         <v>9</v>
       </c>
       <c r="L16" s="33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L16" si="16">CONCATENATE("", C16)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M16" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M16" si="17">CONCATENATE("", D16)</f>
         <v>Elementos.Gases</v>
       </c>
       <c r="N16" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="N16" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
         <v>Peças Gás</v>
       </c>
       <c r="O16" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Cilindro.de.Gás</v>
+        <f t="shared" si="15"/>
+        <v>Medidor.de.Gás</v>
       </c>
       <c r="P16" s="52" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q16" s="52" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="R16" s="30" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="S16" s="30" t="s">
         <v>9</v>
@@ -3895,24 +4142,24 @@
         <v>101</v>
       </c>
       <c r="V16" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="V16" si="19">SUBSTITUTE(E16, "_", " ")</f>
         <v>Peças.Gás</v>
       </c>
       <c r="W16" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X16" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-16</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="Z16" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
-        <v>104</v>
+        <v>183</v>
       </c>
       <c r="AB16" s="63" t="s">
         <v>9</v>
@@ -3924,7 +4171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -3941,7 +4188,7 @@
         <v>117</v>
       </c>
       <c r="F17" s="42" t="s">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="G17" s="60" t="s">
         <v>9</v>
@@ -3959,29 +4206,29 @@
         <v>9</v>
       </c>
       <c r="L17" s="33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M17" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N17" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>Peças Gás</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Tanque.de.Gás</v>
+        <f t="shared" si="15"/>
+        <v>Acessório.de.Gás</v>
       </c>
       <c r="P17" s="52" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q17" s="52" t="s">
-        <v>224</v>
+        <v>142</v>
       </c>
       <c r="R17" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="S17" s="30" t="s">
         <v>9</v>
@@ -3993,24 +4240,24 @@
         <v>101</v>
       </c>
       <c r="V17" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W17" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X17" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-17</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="Z17" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
-        <v>104</v>
+        <v>184</v>
       </c>
       <c r="AB17" s="63" t="s">
         <v>9</v>
@@ -4022,7 +4269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -4036,10 +4283,10 @@
         <v>227</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>225</v>
+        <v>117</v>
       </c>
       <c r="F18" s="42" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G18" s="60" t="s">
         <v>9</v>
@@ -4057,29 +4304,29 @@
         <v>9</v>
       </c>
       <c r="L18" s="33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M18" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N18" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>Gás Doméstico</v>
+        <f t="shared" si="3"/>
+        <v>Peças Gás</v>
       </c>
       <c r="O18" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Aquecedor.a.Gás</v>
+        <f t="shared" si="15"/>
+        <v>Buchão.de.Gás</v>
       </c>
       <c r="P18" s="52" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="Q18" s="52" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="R18" s="30" t="s">
-        <v>218</v>
+        <v>143</v>
       </c>
       <c r="S18" s="30" t="s">
         <v>9</v>
@@ -4091,24 +4338,24 @@
         <v>101</v>
       </c>
       <c r="V18" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Gás.Doméstico</v>
+        <f t="shared" si="5"/>
+        <v>Peças.Gás</v>
       </c>
       <c r="W18" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X18" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-18</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>154</v>
+        <v>238</v>
       </c>
       <c r="Z18" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AB18" s="63" t="s">
         <v>9</v>
@@ -4120,7 +4367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="57">
         <v>19</v>
       </c>
@@ -4134,10 +4381,10 @@
         <v>227</v>
       </c>
       <c r="E19" s="42" t="s">
-        <v>225</v>
+        <v>117</v>
       </c>
       <c r="F19" s="42" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G19" s="60" t="s">
         <v>9</v>
@@ -4155,29 +4402,29 @@
         <v>9</v>
       </c>
       <c r="L19" s="33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M19" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N19" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>Gás Doméstico</v>
+        <f t="shared" si="3"/>
+        <v>Peças Gás</v>
       </c>
       <c r="O19" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Boiler.a.Gás</v>
+        <f t="shared" si="15"/>
+        <v>Cilindro.de.Gás</v>
       </c>
       <c r="P19" s="52" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="Q19" s="52" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="R19" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="S19" s="30" t="s">
         <v>9</v>
@@ -4189,24 +4436,24 @@
         <v>101</v>
       </c>
       <c r="V19" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Gás.Doméstico</v>
+        <f t="shared" si="5"/>
+        <v>Peças.Gás</v>
       </c>
       <c r="W19" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X19" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-19</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>154</v>
+        <v>238</v>
       </c>
       <c r="Z19" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AB19" s="63" t="s">
         <v>9</v>
@@ -4218,7 +4465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="57">
         <v>20</v>
       </c>
@@ -4232,10 +4479,10 @@
         <v>227</v>
       </c>
       <c r="E20" s="42" t="s">
-        <v>225</v>
+        <v>117</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G20" s="60" t="s">
         <v>9</v>
@@ -4253,29 +4500,29 @@
         <v>9</v>
       </c>
       <c r="L20" s="33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N20" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>Gás Doméstico</v>
+        <f t="shared" si="3"/>
+        <v>Peças Gás</v>
       </c>
       <c r="O20" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Caldeira.a.Gás</v>
+        <f t="shared" si="15"/>
+        <v>Tanque.de.Gás</v>
       </c>
       <c r="P20" s="52" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q20" s="52" t="s">
-        <v>146</v>
+        <v>224</v>
       </c>
       <c r="R20" s="30" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="S20" s="30" t="s">
         <v>9</v>
@@ -4287,24 +4534,24 @@
         <v>101</v>
       </c>
       <c r="V20" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Gás.Doméstico</v>
+        <f t="shared" si="5"/>
+        <v>Peças.Gás</v>
       </c>
       <c r="W20" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X20" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-20</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>154</v>
+        <v>238</v>
       </c>
       <c r="Z20" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AB20" s="63" t="s">
         <v>9</v>
@@ -4316,7 +4563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="57">
         <v>21</v>
       </c>
@@ -4333,7 +4580,7 @@
         <v>225</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G21" s="60" t="s">
         <v>9</v>
@@ -4351,29 +4598,29 @@
         <v>9</v>
       </c>
       <c r="L21" s="33" t="str">
-        <f t="shared" ref="L21" si="19">CONCATENATE("", C21)</f>
+        <f t="shared" si="1"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M21" s="33" t="str">
-        <f t="shared" ref="M21" si="20">CONCATENATE("", D21)</f>
+        <f t="shared" si="2"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N21" s="33" t="str">
-        <f t="shared" ref="N21" si="21">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E21),"."," ")," De "," de "))</f>
+        <f t="shared" si="3"/>
         <v>Gás Doméstico</v>
       </c>
       <c r="O21" s="30" t="str">
-        <f t="shared" ref="O21" si="22">IF(ISNUMBER(FIND("Ifc",F21)),CONCATENATE("Classe IFC:   ",F21),CONCATENATE("",F21))</f>
-        <v>Tubulação.Gás</v>
+        <f t="shared" si="15"/>
+        <v>Aquecedor.a.Gás</v>
       </c>
       <c r="P21" s="52" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q21" s="52" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="R21" s="30" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="S21" s="30" t="s">
         <v>9</v>
@@ -4385,24 +4632,24 @@
         <v>101</v>
       </c>
       <c r="V21" s="30" t="str">
-        <f t="shared" ref="V21" si="23">SUBSTITUTE(E21, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Gás.Doméstico</v>
       </c>
       <c r="W21" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X21" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-21</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="Z21" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA21" s="29" t="s">
-        <v>239</v>
+        <v>105</v>
       </c>
       <c r="AB21" s="63" t="s">
         <v>9</v>
@@ -4414,7 +4661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="57">
         <v>22</v>
       </c>
@@ -4428,10 +4675,10 @@
         <v>227</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="G22" s="60" t="s">
         <v>9</v>
@@ -4449,29 +4696,29 @@
         <v>9</v>
       </c>
       <c r="L22" s="33" t="str">
-        <f t="shared" ref="L22:L24" si="24">CONCATENATE("", C22)</f>
+        <f t="shared" si="1"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M22" s="33" t="str">
-        <f t="shared" ref="M22:M24" si="25">CONCATENATE("", D22)</f>
+        <f t="shared" si="2"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N22" s="33" t="str">
-        <f t="shared" ref="N22:N24" si="26">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E22),"."," ")," De "," de "))</f>
-        <v>Gás Hospitalar</v>
+        <f t="shared" si="3"/>
+        <v>Gás Doméstico</v>
       </c>
       <c r="O22" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Aquecedor.a.Gás.Hospitalar</v>
+        <f t="shared" si="15"/>
+        <v>Boiler.a.Gás</v>
       </c>
       <c r="P22" s="52" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="Q22" s="52" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="R22" s="30" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="S22" s="30" t="s">
         <v>9</v>
@@ -4483,14 +4730,14 @@
         <v>101</v>
       </c>
       <c r="V22" s="30" t="str">
-        <f t="shared" ref="V22:V24" si="27">SUBSTITUTE(E22, "_", " ")</f>
-        <v>Gás.Hospitalar</v>
+        <f t="shared" si="5"/>
+        <v>Gás.Doméstico</v>
       </c>
       <c r="W22" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-22</v>
       </c>
       <c r="Y22" s="29" t="s">
@@ -4506,13 +4753,13 @@
         <v>9</v>
       </c>
       <c r="AC22" s="30" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AD22" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="57">
         <v>23</v>
       </c>
@@ -4526,10 +4773,10 @@
         <v>227</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F23" s="42" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="G23" s="60" t="s">
         <v>9</v>
@@ -4547,29 +4794,29 @@
         <v>9</v>
       </c>
       <c r="L23" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="1"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="33" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="2"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N23" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>Gás Hospitalar</v>
+        <f t="shared" si="3"/>
+        <v>Gás Doméstico</v>
       </c>
       <c r="O23" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Boiler.a.Gás.Hospitalar</v>
+        <f t="shared" si="15"/>
+        <v>Caldeira.a.Gás</v>
       </c>
       <c r="P23" s="52" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="Q23" s="52" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="R23" s="30" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="S23" s="30" t="s">
         <v>9</v>
@@ -4581,14 +4828,14 @@
         <v>101</v>
       </c>
       <c r="V23" s="30" t="str">
-        <f t="shared" si="27"/>
-        <v>Gás.Hospitalar</v>
+        <f t="shared" si="5"/>
+        <v>Gás.Doméstico</v>
       </c>
       <c r="W23" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X23" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-23</v>
       </c>
       <c r="Y23" s="29" t="s">
@@ -4598,19 +4845,19 @@
         <v>9</v>
       </c>
       <c r="AA23" s="29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AB23" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC23" s="30" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AD23" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="57">
         <v>24</v>
       </c>
@@ -4624,10 +4871,10 @@
         <v>227</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>193</v>
+        <v>121</v>
       </c>
       <c r="G24" s="60" t="s">
         <v>9</v>
@@ -4645,29 +4892,29 @@
         <v>9</v>
       </c>
       <c r="L24" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="L24" si="20">CONCATENATE("", C24)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="33" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="M24" si="21">CONCATENATE("", D24)</f>
         <v>Elementos.Gases</v>
       </c>
       <c r="N24" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>Gás Hospitalar</v>
+        <f t="shared" ref="N24" si="22">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E24),"."," ")," De "," de "))</f>
+        <v>Gás Doméstico</v>
       </c>
       <c r="O24" s="30" t="str">
-        <f t="shared" si="14"/>
-        <v>Caldeira.a.Gás.Hospitalar</v>
+        <f t="shared" ref="O24" si="23">IF(ISNUMBER(FIND("Ifc",F24)),CONCATENATE("Classe IFC:   ",F24),CONCATENATE("",F24))</f>
+        <v>Tubulação.Gás</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>197</v>
+        <v>129</v>
       </c>
       <c r="Q24" s="52" t="s">
-        <v>201</v>
+        <v>145</v>
       </c>
       <c r="R24" s="30" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="S24" s="30" t="s">
         <v>9</v>
@@ -4679,36 +4926,36 @@
         <v>101</v>
       </c>
       <c r="V24" s="30" t="str">
-        <f t="shared" si="27"/>
-        <v>Gás.Hospitalar</v>
+        <f t="shared" ref="V24" si="24">SUBSTITUTE(E24, "_", " ")</f>
+        <v>Gás.Doméstico</v>
       </c>
       <c r="W24" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X24" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-24</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>154</v>
+        <v>238</v>
       </c>
       <c r="Z24" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="29" t="s">
-        <v>106</v>
+        <v>239</v>
       </c>
       <c r="AB24" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AC24" s="30" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AD24" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="57">
         <v>25</v>
       </c>
@@ -4725,7 +4972,7 @@
         <v>226</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G25" s="60" t="s">
         <v>9</v>
@@ -4743,29 +4990,29 @@
         <v>9</v>
       </c>
       <c r="L25" s="33" t="str">
-        <f t="shared" ref="L25" si="28">CONCATENATE("", C25)</f>
+        <f t="shared" ref="L25:L27" si="25">CONCATENATE("", C25)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M25" s="33" t="str">
-        <f t="shared" ref="M25" si="29">CONCATENATE("", D25)</f>
+        <f t="shared" ref="M25:M27" si="26">CONCATENATE("", D25)</f>
         <v>Elementos.Gases</v>
       </c>
       <c r="N25" s="33" t="str">
-        <f t="shared" ref="N25" si="30">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E25),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N25:N27" si="27">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E25),"."," ")," De "," de "))</f>
         <v>Gás Hospitalar</v>
       </c>
       <c r="O25" s="30" t="str">
-        <f t="shared" ref="O25" si="31">IF(ISNUMBER(FIND("Ifc",F25)),CONCATENATE("Classe IFC:   ",F25),CONCATENATE("",F25))</f>
-        <v>Tubulação.Gás.Hospitalar</v>
+        <f t="shared" si="15"/>
+        <v>Aquecedor.a.Gás.Hospitalar</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q25" s="52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R25" s="30" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="S25" s="30" t="s">
         <v>9</v>
@@ -4777,24 +5024,24 @@
         <v>101</v>
       </c>
       <c r="V25" s="30" t="str">
-        <f t="shared" ref="V25" si="32">SUBSTITUTE(E25, "_", " ")</f>
+        <f t="shared" ref="V25:V27" si="28">SUBSTITUTE(E25, "_", " ")</f>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="W25" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X25" s="58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Key-GAS-25</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="Z25" s="63" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="29" t="s">
-        <v>239</v>
+        <v>105</v>
       </c>
       <c r="AB25" s="63" t="s">
         <v>9</v>
@@ -4806,545 +5053,852 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="57">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="G26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L26" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M26" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N26" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O26" s="30" t="str">
+        <f t="shared" si="15"/>
+        <v>Boiler.a.Gás.Hospitalar</v>
+      </c>
+      <c r="P26" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q26" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="R26" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="S26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T26" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="U26" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V26" s="30" t="str">
+        <f t="shared" si="28"/>
+        <v>Gás.Hospitalar</v>
+      </c>
+      <c r="W26" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X26" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-GAS-26</v>
+      </c>
+      <c r="Y26" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z26" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA26" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB26" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC26" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="AD26" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="57">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="G27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M27" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N27" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O27" s="30" t="str">
+        <f t="shared" si="15"/>
+        <v>Caldeira.a.Gás.Hospitalar</v>
+      </c>
+      <c r="P27" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q27" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="R27" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="S27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T27" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="U27" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V27" s="30" t="str">
+        <f t="shared" si="28"/>
+        <v>Gás.Hospitalar</v>
+      </c>
+      <c r="W27" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X27" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-GAS-27</v>
+      </c>
+      <c r="Y27" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z27" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA27" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB27" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC27" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="AD27" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="57">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="G28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="33" t="str">
+        <f t="shared" ref="L28" si="29">CONCATENATE("", C28)</f>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M28" s="33" t="str">
+        <f t="shared" ref="M28" si="30">CONCATENATE("", D28)</f>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N28" s="33" t="str">
+        <f t="shared" ref="N28" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E28),"."," ")," De "," de "))</f>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O28" s="30" t="str">
+        <f t="shared" ref="O28" si="32">IF(ISNUMBER(FIND("Ifc",F28)),CONCATENATE("Classe IFC:   ",F28),CONCATENATE("",F28))</f>
+        <v>Tubulação.Gás.Hospitalar</v>
+      </c>
+      <c r="P28" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q28" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="R28" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="S28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T28" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="U28" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V28" s="30" t="str">
+        <f t="shared" ref="V28" si="33">SUBSTITUTE(E28, "_", " ")</f>
+        <v>Gás.Hospitalar</v>
+      </c>
+      <c r="W28" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X28" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-GAS-28</v>
+      </c>
+      <c r="Y28" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z28" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="AB28" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="AD28" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="57">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C29" s="65" t="s">
         <v>247</v>
       </c>
-      <c r="D26" s="65" t="s">
+      <c r="D29" s="65" t="s">
         <v>249</v>
       </c>
-      <c r="E26" s="65" t="s">
+      <c r="E29" s="65" t="s">
         <v>248</v>
       </c>
-      <c r="F26" s="65" t="s">
+      <c r="F29" s="65" t="s">
         <v>250</v>
       </c>
-      <c r="G26" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J26" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L26" s="33" t="str">
-        <f t="shared" ref="L26:O30" si="33">SUBSTITUTE(CONCATENATE("", C26), ".", " ")</f>
+      <c r="G29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L29" s="33" t="str">
+        <f t="shared" ref="L29:O33" si="34">SUBSTITUTE(CONCATENATE("", C29), ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="M26" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Macros</v>
-      </c>
-      <c r="N26" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O26" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P26" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q26" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="R26" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="S26" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T26" s="30" t="str">
-        <f t="shared" ref="T26:V30" si="34">SUBSTITUTE(C26, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U26" s="30" t="str">
+      <c r="M29" s="33" t="str">
         <f t="shared" si="34"/>
         <v>Macros</v>
       </c>
-      <c r="V26" s="62" t="str">
+      <c r="N29" s="33" t="str">
         <f t="shared" si="34"/>
         <v>Métodos</v>
       </c>
-      <c r="W26" s="30" t="s">
+      <c r="O29" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P29" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q29" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="R29" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="S29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T29" s="30" t="str">
+        <f t="shared" ref="T29:V33" si="35">SUBSTITUTE(C29, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U29" s="30" t="str">
+        <f t="shared" si="35"/>
+        <v>Macros</v>
+      </c>
+      <c r="V29" s="62" t="str">
+        <f t="shared" si="35"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W29" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="X26" s="58" t="str">
-        <f t="shared" si="5"/>
-        <v>Key-GAS-26</v>
-      </c>
-      <c r="Y26" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z26" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA26" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB26" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC26" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD26" s="63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="57">
-        <v>27</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="X29" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-GAS-29</v>
+      </c>
+      <c r="Y29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD29" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="57">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="C30" s="65" t="s">
         <v>247</v>
       </c>
-      <c r="D27" s="65" t="s">
+      <c r="D30" s="65" t="s">
         <v>249</v>
       </c>
-      <c r="E27" s="65" t="s">
+      <c r="E30" s="65" t="s">
         <v>248</v>
       </c>
-      <c r="F27" s="65" t="s">
+      <c r="F30" s="65" t="s">
         <v>254</v>
       </c>
-      <c r="G27" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L27" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>De API</v>
-      </c>
-      <c r="M27" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Macros</v>
-      </c>
-      <c r="N27" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O27" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P27" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q27" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="R27" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="S27" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T27" s="30" t="str">
+      <c r="G30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L30" s="33" t="str">
         <f t="shared" si="34"/>
         <v>De API</v>
       </c>
-      <c r="U27" s="30" t="str">
+      <c r="M30" s="33" t="str">
         <f t="shared" si="34"/>
         <v>Macros</v>
       </c>
-      <c r="V27" s="62" t="str">
+      <c r="N30" s="33" t="str">
         <f t="shared" si="34"/>
         <v>Métodos</v>
       </c>
-      <c r="W27" s="30" t="s">
+      <c r="O30" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P30" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q30" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="R30" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="S30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T30" s="30" t="str">
+        <f t="shared" si="35"/>
+        <v>De API</v>
+      </c>
+      <c r="U30" s="30" t="str">
+        <f t="shared" si="35"/>
+        <v>Macros</v>
+      </c>
+      <c r="V30" s="62" t="str">
+        <f t="shared" si="35"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W30" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="X27" s="58" t="str">
-        <f t="shared" si="5"/>
-        <v>Key-GAS-27</v>
-      </c>
-      <c r="Y27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD27" s="63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="57">
-        <v>28</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="X30" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-GAS-30</v>
+      </c>
+      <c r="Y30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD30" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="57">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C28" s="65" t="s">
+      <c r="C31" s="65" t="s">
         <v>247</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D31" s="65" t="s">
         <v>249</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E31" s="65" t="s">
         <v>248</v>
       </c>
-      <c r="F28" s="65" t="s">
+      <c r="F31" s="65" t="s">
         <v>258</v>
       </c>
-      <c r="G28" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L28" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>De API</v>
-      </c>
-      <c r="M28" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Macros</v>
-      </c>
-      <c r="N28" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O28" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P28" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q28" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="R28" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="S28" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T28" s="30" t="str">
+      <c r="G31" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L31" s="33" t="str">
         <f t="shared" si="34"/>
         <v>De API</v>
       </c>
-      <c r="U28" s="30" t="str">
+      <c r="M31" s="33" t="str">
         <f t="shared" si="34"/>
         <v>Macros</v>
       </c>
-      <c r="V28" s="62" t="str">
+      <c r="N31" s="33" t="str">
         <f t="shared" si="34"/>
         <v>Métodos</v>
       </c>
-      <c r="W28" s="30" t="s">
+      <c r="O31" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P31" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q31" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="R31" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="S31" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T31" s="30" t="str">
+        <f t="shared" si="35"/>
+        <v>De API</v>
+      </c>
+      <c r="U31" s="30" t="str">
+        <f t="shared" si="35"/>
+        <v>Macros</v>
+      </c>
+      <c r="V31" s="62" t="str">
+        <f t="shared" si="35"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W31" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="X28" s="58" t="str">
-        <f t="shared" si="5"/>
-        <v>Key-GAS-28</v>
-      </c>
-      <c r="Y28" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z28" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA28" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB28" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC28" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD28" s="63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="57">
-        <v>29</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="X31" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-GAS-31</v>
+      </c>
+      <c r="Y31" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z31" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA31" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB31" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD31" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="57">
+        <v>32</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C29" s="65" t="s">
+      <c r="C32" s="65" t="s">
         <v>247</v>
       </c>
-      <c r="D29" s="65" t="s">
+      <c r="D32" s="65" t="s">
         <v>249</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E32" s="65" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="65" t="s">
+      <c r="F32" s="65" t="s">
         <v>262</v>
       </c>
-      <c r="G29" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J29" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K29" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L29" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>De API</v>
-      </c>
-      <c r="M29" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Macros</v>
-      </c>
-      <c r="N29" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O29" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P29" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q29" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="R29" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="S29" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T29" s="30" t="str">
+      <c r="G32" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K32" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" s="33" t="str">
         <f t="shared" si="34"/>
         <v>De API</v>
       </c>
-      <c r="U29" s="30" t="str">
+      <c r="M32" s="33" t="str">
         <f t="shared" si="34"/>
         <v>Macros</v>
       </c>
-      <c r="V29" s="62" t="str">
+      <c r="N32" s="33" t="str">
         <f t="shared" si="34"/>
         <v>Métodos</v>
       </c>
-      <c r="W29" s="30" t="s">
+      <c r="O32" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P32" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q32" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="R32" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="S32" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T32" s="30" t="str">
+        <f t="shared" si="35"/>
+        <v>De API</v>
+      </c>
+      <c r="U32" s="30" t="str">
+        <f t="shared" si="35"/>
+        <v>Macros</v>
+      </c>
+      <c r="V32" s="62" t="str">
+        <f t="shared" si="35"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W32" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="X29" s="58" t="str">
-        <f t="shared" si="5"/>
-        <v>Key-GAS-29</v>
-      </c>
-      <c r="Y29" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z29" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA29" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB29" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC29" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD29" s="63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="57">
-        <v>30</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="X32" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-GAS-32</v>
+      </c>
+      <c r="Y32" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z32" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA32" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB32" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC32" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD32" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="57">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C30" s="65" t="s">
+      <c r="C33" s="65" t="s">
         <v>247</v>
       </c>
-      <c r="D30" s="65" t="s">
+      <c r="D33" s="65" t="s">
         <v>249</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E33" s="65" t="s">
         <v>266</v>
       </c>
-      <c r="F30" s="65" t="s">
+      <c r="F33" s="65" t="s">
         <v>267</v>
       </c>
-      <c r="G30" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I30" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J30" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K30" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L30" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>De API</v>
-      </c>
-      <c r="M30" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Macros</v>
-      </c>
-      <c r="N30" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O30" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P30" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q30" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="R30" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="S30" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T30" s="30" t="str">
+      <c r="G33" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L33" s="33" t="str">
         <f t="shared" si="34"/>
         <v>De API</v>
       </c>
-      <c r="U30" s="30" t="str">
+      <c r="M33" s="33" t="str">
         <f t="shared" si="34"/>
         <v>Macros</v>
       </c>
-      <c r="V30" s="62" t="str">
+      <c r="N33" s="33" t="str">
         <f t="shared" si="34"/>
         <v>Códigos Visuais</v>
       </c>
-      <c r="W30" s="30" t="s">
+      <c r="O33" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P33" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q33" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="R33" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="S33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T33" s="30" t="str">
+        <f t="shared" si="35"/>
+        <v>De API</v>
+      </c>
+      <c r="U33" s="30" t="str">
+        <f t="shared" si="35"/>
+        <v>Macros</v>
+      </c>
+      <c r="V33" s="62" t="str">
+        <f t="shared" si="35"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W33" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="X30" s="58" t="str">
-        <f t="shared" si="5"/>
-        <v>Key-GAS-30</v>
-      </c>
-      <c r="Y30" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z30" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA30" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB30" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC30" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD30" s="63" t="s">
+      <c r="X33" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-GAS-33</v>
+      </c>
+      <c r="Y33" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z33" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA33" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB33" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC33" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD33" s="63" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC886">
-    <sortCondition ref="F2:F886"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AC889">
+    <sortCondition ref="F5:F889"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B30">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+  <conditionalFormatting sqref="B5:B33">
+    <cfRule type="cellIs" dxfId="36" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:D1 F1:O1 R1:Z1 AB1:AD1">
-    <cfRule type="cellIs" dxfId="17" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="90" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E30:F30">
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+  <conditionalFormatting sqref="E33:F33">
+    <cfRule type="duplicateValues" dxfId="34" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="15" priority="1506"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1526"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10:F25 F1:F2 F31:F1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="1528"/>
+  <conditionalFormatting sqref="F13:F28 F1 F34:F1048576 F5">
+    <cfRule type="duplicateValues" dxfId="32" priority="1548"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26:F29">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+  <conditionalFormatting sqref="F29:F32">
+    <cfRule type="duplicateValues" dxfId="31" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1478"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1499"/>
+  <conditionalFormatting sqref="F34:F1048576">
+    <cfRule type="duplicateValues" dxfId="30" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1498"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1519"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
-    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
+  <conditionalFormatting sqref="R5:R28">
+    <cfRule type="cellIs" dxfId="26" priority="35" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y4 AA2:AA4 AC2:AC4 R2:R4 A2:B2 B3:B4 A3:A33">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F4">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
@@ -5352,18 +5906,371 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877C8151-860E-49B4-BC4C-3C22E304B5AB}">
+  <dimension ref="A1:AD3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.53515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.61328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="76.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="73.921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="66.921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.921875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.69140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.4609375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.61328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.765625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="1.921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" s="53" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="57" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", C1), ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M1" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", D1), ".", " ")</f>
+        <v>Materialidades</v>
+      </c>
+      <c r="N1" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", E1), ".", " ")</f>
+        <v>Materiais</v>
+      </c>
+      <c r="O1" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", F1), ".", " ")</f>
+        <v>Tubo de Aço Costura</v>
+      </c>
+      <c r="P1" s="66" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q1" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="R1" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="S1" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T1" s="30" t="str">
+        <f>SUBSTITUTE(C1, ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U1" s="30" t="str">
+        <f>SUBSTITUTE(D1, ".", " ")</f>
+        <v>Materialidades</v>
+      </c>
+      <c r="V1" s="30" t="str">
+        <f>SUBSTITUTE(E1, ".", " ")</f>
+        <v>Materiais</v>
+      </c>
+      <c r="W1" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X1" s="58" t="str">
+        <f>CONCATENATE("Key-TUB-",A1)</f>
+        <v>Key-TUB-c</v>
+      </c>
+      <c r="Y1" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z1" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA1" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB1" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC1" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="AD1" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" s="53" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="57">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="G2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", C2), ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M2" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", D2), ".", " ")</f>
+        <v>Materialidades</v>
+      </c>
+      <c r="N2" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", E2), ".", " ")</f>
+        <v>Materiais</v>
+      </c>
+      <c r="O2" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", F2), ".", " ")</f>
+        <v>Tubo de Cobre</v>
+      </c>
+      <c r="P2" s="66" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="S2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="30" t="str">
+        <f>SUBSTITUTE(C2, ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U2" s="30" t="str">
+        <f>SUBSTITUTE(D2, ".", " ")</f>
+        <v>Materialidades</v>
+      </c>
+      <c r="V2" s="30" t="str">
+        <f>SUBSTITUTE(E2, ".", " ")</f>
+        <v>Materiais</v>
+      </c>
+      <c r="W2" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X2" s="58" t="str">
+        <f>CONCATENATE("Key-TUB-",A2)</f>
+        <v>Key-TUB-2</v>
+      </c>
+      <c r="Y2" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z2" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB2" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="AD2" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" s="53" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="57">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F3" s="56" t="s">
+        <v>284</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", C3), ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M3" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", D3), ".", " ")</f>
+        <v>Materialidades</v>
+      </c>
+      <c r="N3" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", E3), ".", " ")</f>
+        <v>Materiais</v>
+      </c>
+      <c r="O3" s="33" t="str">
+        <f>SUBSTITUTE(CONCATENATE("", F3), ".", " ")</f>
+        <v>Tubo Multicamada</v>
+      </c>
+      <c r="P3" s="66" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="30" t="str">
+        <f>SUBSTITUTE(C3, ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U3" s="30" t="str">
+        <f>SUBSTITUTE(D3, ".", " ")</f>
+        <v>Materialidades</v>
+      </c>
+      <c r="V3" s="30" t="str">
+        <f>SUBSTITUTE(E3, ".", " ")</f>
+        <v>Materiais</v>
+      </c>
+      <c r="W3" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X3" s="58" t="str">
+        <f>CONCATENATE("Key-TUB-",A3)</f>
+        <v>Key-TUB-3</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z3" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB3" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="AD3" s="63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:AD3">
+    <sortCondition ref="F1:F3"/>
+  </sortState>
+  <conditionalFormatting sqref="Y1:Y3 AA1:AA3 AC1:AC3 R1:R3 A1:B3">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F3">
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5428,7 +6335,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5493,7 +6400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5560,7 +6467,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5572,34 +6479,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.53515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="62" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.3046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.3046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.53515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.15234375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -5658,7 +6565,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>1</v>
       </c>
@@ -5717,7 +6624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>2</v>
       </c>
@@ -5776,7 +6683,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>3</v>
       </c>
@@ -5835,7 +6742,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>4</v>
       </c>
@@ -5897,25 +6804,25 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="6" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1495"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -5938,7 +6845,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -5967,22 +6874,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Gases.xlsx
+++ b/Versão5/SIS/Ontologia_Gases.xlsx
@@ -1502,131 +1502,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="29">
     <dxf>
       <font>
         <b val="0"/>
@@ -1761,6 +1637,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1841,11 +1725,53 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2491,7 +2417,7 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46270.453988657406</v>
+        <v>46270.88738148148</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>88</v>
@@ -2730,19 +2656,19 @@
         <v>9</v>
       </c>
       <c r="L2" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", C2), ".", " ")</f>
+        <f t="shared" ref="L2:O4" si="0">SUBSTITUTE(CONCATENATE("", C2), ".", " ")</f>
         <v>De Materialidade</v>
       </c>
       <c r="M2" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", D2), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materialidades</v>
       </c>
       <c r="N2" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", E2), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materiais</v>
       </c>
       <c r="O2" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", F2), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Tubo de Aço Costura</v>
       </c>
       <c r="P2" s="66" t="s">
@@ -2758,22 +2684,22 @@
         <v>9</v>
       </c>
       <c r="T2" s="30" t="str">
-        <f>SUBSTITUTE(C2, ".", " ")</f>
+        <f t="shared" ref="T2:V4" si="1">SUBSTITUTE(C2, ".", " ")</f>
         <v>De Materialidade</v>
       </c>
       <c r="U2" s="30" t="str">
-        <f>SUBSTITUTE(D2, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materialidades</v>
       </c>
       <c r="V2" s="30" t="str">
-        <f>SUBSTITUTE(E2, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materiais</v>
       </c>
       <c r="W2" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X2" s="58" t="str">
-        <f t="shared" ref="X2:X4" si="0">CONCATENATE("Key-GAS-",A2)</f>
+        <f t="shared" ref="X2:X4" si="2">CONCATENATE("Key-GAS-",A2)</f>
         <v>Key-GAS-2</v>
       </c>
       <c r="Y2" s="30" t="s">
@@ -2830,19 +2756,19 @@
         <v>9</v>
       </c>
       <c r="L3" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", C3), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>De Materialidade</v>
       </c>
       <c r="M3" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", D3), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materialidades</v>
       </c>
       <c r="N3" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", E3), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materiais</v>
       </c>
       <c r="O3" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", F3), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Tubo de Cobre</v>
       </c>
       <c r="P3" s="66" t="s">
@@ -2858,22 +2784,22 @@
         <v>9</v>
       </c>
       <c r="T3" s="30" t="str">
-        <f>SUBSTITUTE(C3, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>De Materialidade</v>
       </c>
       <c r="U3" s="30" t="str">
-        <f>SUBSTITUTE(D3, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materialidades</v>
       </c>
       <c r="V3" s="30" t="str">
-        <f>SUBSTITUTE(E3, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materiais</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X3" s="58" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Key-GAS-3</v>
       </c>
       <c r="Y3" s="30" t="s">
@@ -2930,19 +2856,19 @@
         <v>9</v>
       </c>
       <c r="L4" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", C4), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>De Materialidade</v>
       </c>
       <c r="M4" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", D4), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materialidades</v>
       </c>
       <c r="N4" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", E4), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materiais</v>
       </c>
       <c r="O4" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", F4), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Tubo Multicamada</v>
       </c>
       <c r="P4" s="66" t="s">
@@ -2958,22 +2884,22 @@
         <v>9</v>
       </c>
       <c r="T4" s="30" t="str">
-        <f>SUBSTITUTE(C4, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>De Materialidade</v>
       </c>
       <c r="U4" s="30" t="str">
-        <f>SUBSTITUTE(D4, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materialidades</v>
       </c>
       <c r="V4" s="30" t="str">
-        <f>SUBSTITUTE(E4, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materiais</v>
       </c>
       <c r="W4" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X4" s="58" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Key-GAS-4</v>
       </c>
       <c r="Y4" s="30" t="s">
@@ -3030,19 +2956,19 @@
         <v>9</v>
       </c>
       <c r="L5" s="33" t="str">
-        <f t="shared" ref="L5:L23" si="1">CONCATENATE("", C5)</f>
+        <f t="shared" ref="L5:L23" si="3">CONCATENATE("", C5)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M5" s="33" t="str">
-        <f t="shared" ref="M5:M23" si="2">CONCATENATE("", D5)</f>
+        <f t="shared" ref="M5:M23" si="4">CONCATENATE("", D5)</f>
         <v>Sistema.Gases</v>
       </c>
       <c r="N5" s="33" t="str">
-        <f t="shared" ref="N5:N23" si="3">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E5),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N5:N23" si="5">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E5),"."," ")," De "," de "))</f>
         <v>Sistema de Gás</v>
       </c>
       <c r="O5" s="30" t="str">
-        <f t="shared" ref="O5:O12" si="4">IF(ISNUMBER(FIND("Ifc",F5)),CONCATENATE("Classe IFC:   ",F5),CONCATENATE("",F5))</f>
+        <f t="shared" ref="O5:O12" si="6">IF(ISNUMBER(FIND("Ifc",F5)),CONCATENATE("Classe IFC:   ",F5),CONCATENATE("",F5))</f>
         <v>Sistema.GAS</v>
       </c>
       <c r="P5" s="52" t="s">
@@ -3064,14 +2990,14 @@
         <v>101</v>
       </c>
       <c r="V5" s="30" t="str">
-        <f t="shared" ref="V5:V23" si="5">SUBSTITUTE(E5, "_", " ")</f>
+        <f t="shared" ref="V5:V23" si="7">SUBSTITUTE(E5, "_", " ")</f>
         <v>Sistema.de.Gás</v>
       </c>
       <c r="W5" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X5" s="58" t="str">
-        <f t="shared" ref="X5:X33" si="6">CONCATENATE("Key-GAS-",A5)</f>
+        <f t="shared" ref="X5:X33" si="8">CONCATENATE("Key-GAS-",A5)</f>
         <v>Key-GAS-5</v>
       </c>
       <c r="Y5" s="29" t="s">
@@ -3128,19 +3054,19 @@
         <v>9</v>
       </c>
       <c r="L6" s="33" t="str">
-        <f t="shared" ref="L6:L17" si="7">CONCATENATE("", C6)</f>
+        <f t="shared" ref="L6:L17" si="9">CONCATENATE("", C6)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M6" s="33" t="str">
-        <f t="shared" ref="M6:M17" si="8">CONCATENATE("", D6)</f>
+        <f t="shared" ref="M6:M17" si="10">CONCATENATE("", D6)</f>
         <v>Sistema.Gases</v>
       </c>
       <c r="N6" s="33" t="str">
-        <f t="shared" ref="N6:N17" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N6:N17" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O6" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Oxigênio</v>
       </c>
       <c r="P6" s="52" t="s">
@@ -3162,14 +3088,14 @@
         <v>101</v>
       </c>
       <c r="V6" s="30" t="str">
-        <f t="shared" ref="V6:V17" si="10">SUBSTITUTE(E6, "_", " ")</f>
+        <f t="shared" ref="V6:V17" si="12">SUBSTITUTE(E6, "_", " ")</f>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W6" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-6</v>
       </c>
       <c r="Y6" s="29" t="s">
@@ -3226,19 +3152,19 @@
         <v>9</v>
       </c>
       <c r="L7" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M7" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Sistema.Gases</v>
       </c>
       <c r="N7" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O7" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Ar.Medicinal</v>
       </c>
       <c r="P7" s="52" t="s">
@@ -3260,14 +3186,14 @@
         <v>101</v>
       </c>
       <c r="V7" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W7" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X7" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-7</v>
       </c>
       <c r="Y7" s="29" t="s">
@@ -3324,19 +3250,19 @@
         <v>9</v>
       </c>
       <c r="L8" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M8" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Sistema.Gases</v>
       </c>
       <c r="N8" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O8" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Ar.Comprimido</v>
       </c>
       <c r="P8" s="52" t="s">
@@ -3358,14 +3284,14 @@
         <v>101</v>
       </c>
       <c r="V8" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W8" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X8" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-8</v>
       </c>
       <c r="Y8" s="29" t="s">
@@ -3422,19 +3348,19 @@
         <v>9</v>
       </c>
       <c r="L9" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M9" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Sistema.Gases</v>
       </c>
       <c r="N9" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O9" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Óxido.Nitroso</v>
       </c>
       <c r="P9" s="52" t="s">
@@ -3456,14 +3382,14 @@
         <v>101</v>
       </c>
       <c r="V9" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W9" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X9" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-9</v>
       </c>
       <c r="Y9" s="29" t="s">
@@ -3520,19 +3446,19 @@
         <v>9</v>
       </c>
       <c r="L10" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M10" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Sistema.Gases</v>
       </c>
       <c r="N10" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O10" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Nitrogênio</v>
       </c>
       <c r="P10" s="52" t="s">
@@ -3554,14 +3480,14 @@
         <v>101</v>
       </c>
       <c r="V10" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W10" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X10" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-10</v>
       </c>
       <c r="Y10" s="29" t="s">
@@ -3618,19 +3544,19 @@
         <v>9</v>
       </c>
       <c r="L11" s="33" t="str">
-        <f t="shared" ref="L11" si="11">CONCATENATE("", C11)</f>
+        <f t="shared" ref="L11" si="13">CONCATENATE("", C11)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M11" s="33" t="str">
-        <f t="shared" ref="M11" si="12">CONCATENATE("", D11)</f>
+        <f t="shared" ref="M11" si="14">CONCATENATE("", D11)</f>
         <v>Sistema.Gases</v>
       </c>
       <c r="N11" s="33" t="str">
-        <f t="shared" ref="N11" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N11" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O11" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Hélio</v>
       </c>
       <c r="P11" s="52" t="s">
@@ -3652,14 +3578,14 @@
         <v>101</v>
       </c>
       <c r="V11" s="30" t="str">
-        <f t="shared" ref="V11" si="14">SUBSTITUTE(E11, "_", " ")</f>
+        <f t="shared" ref="V11" si="16">SUBSTITUTE(E11, "_", " ")</f>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X11" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-11</v>
       </c>
       <c r="Y11" s="29" t="s">
@@ -3716,19 +3642,19 @@
         <v>9</v>
       </c>
       <c r="L12" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M12" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Sistema.Gases</v>
       </c>
       <c r="N12" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O12" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Vacuo</v>
       </c>
       <c r="P12" s="52" t="s">
@@ -3750,14 +3676,14 @@
         <v>101</v>
       </c>
       <c r="V12" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="W12" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X12" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-12</v>
       </c>
       <c r="Y12" s="29" t="s">
@@ -3814,15 +3740,15 @@
         <v>9</v>
       </c>
       <c r="L13" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M13" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N13" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Peças Gás</v>
       </c>
       <c r="O13" s="30" t="str">
@@ -3848,14 +3774,14 @@
         <v>101</v>
       </c>
       <c r="V13" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W13" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X13" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-13</v>
       </c>
       <c r="Y13" s="29" t="s">
@@ -3912,19 +3838,19 @@
         <v>9</v>
       </c>
       <c r="L14" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M14" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N14" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Peças Gás</v>
       </c>
       <c r="O14" s="30" t="str">
-        <f t="shared" ref="O14:O27" si="15">IF(ISNUMBER(FIND("Ifc",F14)),CONCATENATE("Classe IFC:   ",F14),CONCATENATE("",F14))</f>
+        <f t="shared" ref="O14:O27" si="17">IF(ISNUMBER(FIND("Ifc",F14)),CONCATENATE("Classe IFC:   ",F14),CONCATENATE("",F14))</f>
         <v>Registro.de.Gás</v>
       </c>
       <c r="P14" s="52" t="s">
@@ -3946,14 +3872,14 @@
         <v>101</v>
       </c>
       <c r="V14" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W14" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X14" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-14</v>
       </c>
       <c r="Y14" s="29" t="s">
@@ -4010,19 +3936,19 @@
         <v>9</v>
       </c>
       <c r="L15" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M15" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N15" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Peças Gás</v>
       </c>
       <c r="O15" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Válvula.de.Gás</v>
       </c>
       <c r="P15" s="52" t="s">
@@ -4044,14 +3970,14 @@
         <v>101</v>
       </c>
       <c r="V15" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W15" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X15" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-15</v>
       </c>
       <c r="Y15" s="29" t="s">
@@ -4108,19 +4034,19 @@
         <v>9</v>
       </c>
       <c r="L16" s="33" t="str">
-        <f t="shared" ref="L16" si="16">CONCATENATE("", C16)</f>
+        <f t="shared" ref="L16" si="18">CONCATENATE("", C16)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M16" s="33" t="str">
-        <f t="shared" ref="M16" si="17">CONCATENATE("", D16)</f>
+        <f t="shared" ref="M16" si="19">CONCATENATE("", D16)</f>
         <v>Elementos.Gases</v>
       </c>
       <c r="N16" s="33" t="str">
-        <f t="shared" ref="N16" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N16" si="20">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
         <v>Peças Gás</v>
       </c>
       <c r="O16" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Medidor.de.Gás</v>
       </c>
       <c r="P16" s="52" t="s">
@@ -4142,14 +4068,14 @@
         <v>101</v>
       </c>
       <c r="V16" s="30" t="str">
-        <f t="shared" ref="V16" si="19">SUBSTITUTE(E16, "_", " ")</f>
+        <f t="shared" ref="V16" si="21">SUBSTITUTE(E16, "_", " ")</f>
         <v>Peças.Gás</v>
       </c>
       <c r="W16" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X16" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-16</v>
       </c>
       <c r="Y16" s="29" t="s">
@@ -4206,19 +4132,19 @@
         <v>9</v>
       </c>
       <c r="L17" s="33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M17" s="33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N17" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Peças Gás</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Acessório.de.Gás</v>
       </c>
       <c r="P17" s="52" t="s">
@@ -4240,14 +4166,14 @@
         <v>101</v>
       </c>
       <c r="V17" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W17" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X17" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-17</v>
       </c>
       <c r="Y17" s="29" t="s">
@@ -4304,19 +4230,19 @@
         <v>9</v>
       </c>
       <c r="L18" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M18" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N18" s="33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Peças Gás</v>
       </c>
       <c r="O18" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Buchão.de.Gás</v>
       </c>
       <c r="P18" s="52" t="s">
@@ -4338,14 +4264,14 @@
         <v>101</v>
       </c>
       <c r="V18" s="30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W18" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X18" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-18</v>
       </c>
       <c r="Y18" s="29" t="s">
@@ -4402,19 +4328,19 @@
         <v>9</v>
       </c>
       <c r="L19" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M19" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N19" s="33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Peças Gás</v>
       </c>
       <c r="O19" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Cilindro.de.Gás</v>
       </c>
       <c r="P19" s="52" t="s">
@@ -4436,14 +4362,14 @@
         <v>101</v>
       </c>
       <c r="V19" s="30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W19" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X19" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-19</v>
       </c>
       <c r="Y19" s="29" t="s">
@@ -4500,19 +4426,19 @@
         <v>9</v>
       </c>
       <c r="L20" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N20" s="33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Peças Gás</v>
       </c>
       <c r="O20" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Tanque.de.Gás</v>
       </c>
       <c r="P20" s="52" t="s">
@@ -4534,14 +4460,14 @@
         <v>101</v>
       </c>
       <c r="V20" s="30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Peças.Gás</v>
       </c>
       <c r="W20" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X20" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-20</v>
       </c>
       <c r="Y20" s="29" t="s">
@@ -4598,19 +4524,19 @@
         <v>9</v>
       </c>
       <c r="L21" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M21" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N21" s="33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Gás Doméstico</v>
       </c>
       <c r="O21" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Aquecedor.a.Gás</v>
       </c>
       <c r="P21" s="52" t="s">
@@ -4632,14 +4558,14 @@
         <v>101</v>
       </c>
       <c r="V21" s="30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Gás.Doméstico</v>
       </c>
       <c r="W21" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X21" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-21</v>
       </c>
       <c r="Y21" s="29" t="s">
@@ -4696,19 +4622,19 @@
         <v>9</v>
       </c>
       <c r="L22" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M22" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N22" s="33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Gás Doméstico</v>
       </c>
       <c r="O22" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Boiler.a.Gás</v>
       </c>
       <c r="P22" s="52" t="s">
@@ -4730,14 +4656,14 @@
         <v>101</v>
       </c>
       <c r="V22" s="30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Gás.Doméstico</v>
       </c>
       <c r="W22" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-22</v>
       </c>
       <c r="Y22" s="29" t="s">
@@ -4794,19 +4720,19 @@
         <v>9</v>
       </c>
       <c r="L23" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N23" s="33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Gás Doméstico</v>
       </c>
       <c r="O23" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Caldeira.a.Gás</v>
       </c>
       <c r="P23" s="52" t="s">
@@ -4828,14 +4754,14 @@
         <v>101</v>
       </c>
       <c r="V23" s="30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Gás.Doméstico</v>
       </c>
       <c r="W23" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X23" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-23</v>
       </c>
       <c r="Y23" s="29" t="s">
@@ -4892,19 +4818,19 @@
         <v>9</v>
       </c>
       <c r="L24" s="33" t="str">
-        <f t="shared" ref="L24" si="20">CONCATENATE("", C24)</f>
+        <f t="shared" ref="L24" si="22">CONCATENATE("", C24)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="33" t="str">
-        <f t="shared" ref="M24" si="21">CONCATENATE("", D24)</f>
+        <f t="shared" ref="M24" si="23">CONCATENATE("", D24)</f>
         <v>Elementos.Gases</v>
       </c>
       <c r="N24" s="33" t="str">
-        <f t="shared" ref="N24" si="22">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E24),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N24" si="24">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E24),"."," ")," De "," de "))</f>
         <v>Gás Doméstico</v>
       </c>
       <c r="O24" s="30" t="str">
-        <f t="shared" ref="O24" si="23">IF(ISNUMBER(FIND("Ifc",F24)),CONCATENATE("Classe IFC:   ",F24),CONCATENATE("",F24))</f>
+        <f t="shared" ref="O24" si="25">IF(ISNUMBER(FIND("Ifc",F24)),CONCATENATE("Classe IFC:   ",F24),CONCATENATE("",F24))</f>
         <v>Tubulação.Gás</v>
       </c>
       <c r="P24" s="52" t="s">
@@ -4926,14 +4852,14 @@
         <v>101</v>
       </c>
       <c r="V24" s="30" t="str">
-        <f t="shared" ref="V24" si="24">SUBSTITUTE(E24, "_", " ")</f>
+        <f t="shared" ref="V24" si="26">SUBSTITUTE(E24, "_", " ")</f>
         <v>Gás.Doméstico</v>
       </c>
       <c r="W24" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X24" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-24</v>
       </c>
       <c r="Y24" s="29" t="s">
@@ -4990,19 +4916,19 @@
         <v>9</v>
       </c>
       <c r="L25" s="33" t="str">
-        <f t="shared" ref="L25:L27" si="25">CONCATENATE("", C25)</f>
+        <f t="shared" ref="L25:L27" si="27">CONCATENATE("", C25)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M25" s="33" t="str">
-        <f t="shared" ref="M25:M27" si="26">CONCATENATE("", D25)</f>
+        <f t="shared" ref="M25:M27" si="28">CONCATENATE("", D25)</f>
         <v>Elementos.Gases</v>
       </c>
       <c r="N25" s="33" t="str">
-        <f t="shared" ref="N25:N27" si="27">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E25),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N25:N27" si="29">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E25),"."," ")," De "," de "))</f>
         <v>Gás Hospitalar</v>
       </c>
       <c r="O25" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Aquecedor.a.Gás.Hospitalar</v>
       </c>
       <c r="P25" s="52" t="s">
@@ -5024,14 +4950,14 @@
         <v>101</v>
       </c>
       <c r="V25" s="30" t="str">
-        <f t="shared" ref="V25:V27" si="28">SUBSTITUTE(E25, "_", " ")</f>
+        <f t="shared" ref="V25:V27" si="30">SUBSTITUTE(E25, "_", " ")</f>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="W25" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X25" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-25</v>
       </c>
       <c r="Y25" s="29" t="s">
@@ -5088,19 +5014,19 @@
         <v>9</v>
       </c>
       <c r="L26" s="33" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M26" s="33" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N26" s="33" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>Gás Hospitalar</v>
       </c>
       <c r="O26" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Boiler.a.Gás.Hospitalar</v>
       </c>
       <c r="P26" s="52" t="s">
@@ -5122,14 +5048,14 @@
         <v>101</v>
       </c>
       <c r="V26" s="30" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="W26" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X26" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-26</v>
       </c>
       <c r="Y26" s="29" t="s">
@@ -5186,19 +5112,19 @@
         <v>9</v>
       </c>
       <c r="L27" s="33" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M27" s="33" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>Elementos.Gases</v>
       </c>
       <c r="N27" s="33" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>Gás Hospitalar</v>
       </c>
       <c r="O27" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Caldeira.a.Gás.Hospitalar</v>
       </c>
       <c r="P27" s="52" t="s">
@@ -5220,14 +5146,14 @@
         <v>101</v>
       </c>
       <c r="V27" s="30" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="W27" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X27" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-27</v>
       </c>
       <c r="Y27" s="29" t="s">
@@ -5284,19 +5210,19 @@
         <v>9</v>
       </c>
       <c r="L28" s="33" t="str">
-        <f t="shared" ref="L28" si="29">CONCATENATE("", C28)</f>
+        <f t="shared" ref="L28" si="31">CONCATENATE("", C28)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M28" s="33" t="str">
-        <f t="shared" ref="M28" si="30">CONCATENATE("", D28)</f>
+        <f t="shared" ref="M28" si="32">CONCATENATE("", D28)</f>
         <v>Elementos.Gases</v>
       </c>
       <c r="N28" s="33" t="str">
-        <f t="shared" ref="N28" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E28),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N28" si="33">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E28),"."," ")," De "," de "))</f>
         <v>Gás Hospitalar</v>
       </c>
       <c r="O28" s="30" t="str">
-        <f t="shared" ref="O28" si="32">IF(ISNUMBER(FIND("Ifc",F28)),CONCATENATE("Classe IFC:   ",F28),CONCATENATE("",F28))</f>
+        <f t="shared" ref="O28" si="34">IF(ISNUMBER(FIND("Ifc",F28)),CONCATENATE("Classe IFC:   ",F28),CONCATENATE("",F28))</f>
         <v>Tubulação.Gás.Hospitalar</v>
       </c>
       <c r="P28" s="52" t="s">
@@ -5318,14 +5244,14 @@
         <v>101</v>
       </c>
       <c r="V28" s="30" t="str">
-        <f t="shared" ref="V28" si="33">SUBSTITUTE(E28, "_", " ")</f>
+        <f t="shared" ref="V28" si="35">SUBSTITUTE(E28, "_", " ")</f>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="W28" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X28" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-28</v>
       </c>
       <c r="Y28" s="29" t="s">
@@ -5382,19 +5308,19 @@
         <v>9</v>
       </c>
       <c r="L29" s="33" t="str">
-        <f t="shared" ref="L29:O33" si="34">SUBSTITUTE(CONCATENATE("", C29), ".", " ")</f>
+        <f t="shared" ref="L29:O33" si="36">SUBSTITUTE(CONCATENATE("", C29), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M29" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Macros</v>
       </c>
       <c r="N29" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Métodos</v>
       </c>
       <c r="O29" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Função Auxiliar</v>
       </c>
       <c r="P29" s="30" t="s">
@@ -5410,22 +5336,22 @@
         <v>9</v>
       </c>
       <c r="T29" s="30" t="str">
-        <f t="shared" ref="T29:V33" si="35">SUBSTITUTE(C29, ".", " ")</f>
+        <f t="shared" ref="T29:V33" si="37">SUBSTITUTE(C29, ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="U29" s="30" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Macros</v>
       </c>
       <c r="V29" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Métodos</v>
       </c>
       <c r="W29" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X29" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-29</v>
       </c>
       <c r="Y29" s="63" t="s">
@@ -5482,19 +5408,19 @@
         <v>9</v>
       </c>
       <c r="L30" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>De API</v>
       </c>
       <c r="M30" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Macros</v>
       </c>
       <c r="N30" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Métodos</v>
       </c>
       <c r="O30" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Função Global</v>
       </c>
       <c r="P30" s="30" t="s">
@@ -5510,22 +5436,22 @@
         <v>9</v>
       </c>
       <c r="T30" s="30" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>De API</v>
       </c>
       <c r="U30" s="30" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Macros</v>
       </c>
       <c r="V30" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Métodos</v>
       </c>
       <c r="W30" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X30" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-30</v>
       </c>
       <c r="Y30" s="63" t="s">
@@ -5582,19 +5508,19 @@
         <v>9</v>
       </c>
       <c r="L31" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>De API</v>
       </c>
       <c r="M31" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Macros</v>
       </c>
       <c r="N31" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Métodos</v>
       </c>
       <c r="O31" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Função Local</v>
       </c>
       <c r="P31" s="30" t="s">
@@ -5610,22 +5536,22 @@
         <v>9</v>
       </c>
       <c r="T31" s="30" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>De API</v>
       </c>
       <c r="U31" s="30" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Macros</v>
       </c>
       <c r="V31" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Métodos</v>
       </c>
       <c r="W31" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X31" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-31</v>
       </c>
       <c r="Y31" s="63" t="s">
@@ -5682,19 +5608,19 @@
         <v>9</v>
       </c>
       <c r="L32" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>De API</v>
       </c>
       <c r="M32" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Macros</v>
       </c>
       <c r="N32" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Métodos</v>
       </c>
       <c r="O32" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Função Filtro</v>
       </c>
       <c r="P32" s="30" t="s">
@@ -5710,22 +5636,22 @@
         <v>9</v>
       </c>
       <c r="T32" s="30" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>De API</v>
       </c>
       <c r="U32" s="30" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Macros</v>
       </c>
       <c r="V32" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Métodos</v>
       </c>
       <c r="W32" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X32" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-32</v>
       </c>
       <c r="Y32" s="63" t="s">
@@ -5782,19 +5708,19 @@
         <v>9</v>
       </c>
       <c r="L33" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>De API</v>
       </c>
       <c r="M33" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Macros</v>
       </c>
       <c r="N33" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Códigos Visuais</v>
       </c>
       <c r="O33" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>Bloco de Código</v>
       </c>
       <c r="P33" s="30" t="s">
@@ -5810,22 +5736,22 @@
         <v>9</v>
       </c>
       <c r="T33" s="30" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>De API</v>
       </c>
       <c r="U33" s="30" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Macros</v>
       </c>
       <c r="V33" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>Códigos Visuais</v>
       </c>
       <c r="W33" s="30" t="s">
         <v>102</v>
       </c>
       <c r="X33" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Key-GAS-33</v>
       </c>
       <c r="Y33" s="63" t="s">
@@ -5852,50 +5778,40 @@
     <sortCondition ref="F5:F889"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B5:B33">
-    <cfRule type="cellIs" dxfId="36" priority="21" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:D1 F1:O1 R1:Z1 AB1:AD1">
-    <cfRule type="cellIs" dxfId="35" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="90" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F33">
-    <cfRule type="duplicateValues" dxfId="34" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="33" priority="1526"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1526"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F4">
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13:F28 F1 F34:F1048576 F5">
-    <cfRule type="duplicateValues" dxfId="32" priority="1548"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F32">
-    <cfRule type="duplicateValues" dxfId="31" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34:F1048576">
-    <cfRule type="duplicateValues" dxfId="30" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="1498"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="1519"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1498"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1519"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R28">
-    <cfRule type="cellIs" dxfId="26" priority="35" operator="equal">
+  <conditionalFormatting sqref="Y2:Y4 AA2:AA4 AC2:AC4 R2:R28 A2:B33">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y4 AA2:AA4 AC2:AC4 R2:R4 A2:B2 B3:B4 A3:A33">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5973,19 +5889,19 @@
         <v>9</v>
       </c>
       <c r="L1" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", C1), ".", " ")</f>
+        <f t="shared" ref="L1:O3" si="0">SUBSTITUTE(CONCATENATE("", C1), ".", " ")</f>
         <v>De Materialidade</v>
       </c>
       <c r="M1" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", D1), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materialidades</v>
       </c>
       <c r="N1" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", E1), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materiais</v>
       </c>
       <c r="O1" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", F1), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Tubo de Aço Costura</v>
       </c>
       <c r="P1" s="66" t="s">
@@ -6001,15 +5917,15 @@
         <v>9</v>
       </c>
       <c r="T1" s="30" t="str">
-        <f>SUBSTITUTE(C1, ".", " ")</f>
+        <f t="shared" ref="T1:V3" si="1">SUBSTITUTE(C1, ".", " ")</f>
         <v>De Materialidade</v>
       </c>
       <c r="U1" s="30" t="str">
-        <f>SUBSTITUTE(D1, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materialidades</v>
       </c>
       <c r="V1" s="30" t="str">
-        <f>SUBSTITUTE(E1, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materiais</v>
       </c>
       <c r="W1" s="30" t="s">
@@ -6073,19 +5989,19 @@
         <v>9</v>
       </c>
       <c r="L2" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", C2), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>De Materialidade</v>
       </c>
       <c r="M2" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", D2), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materialidades</v>
       </c>
       <c r="N2" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", E2), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materiais</v>
       </c>
       <c r="O2" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", F2), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Tubo de Cobre</v>
       </c>
       <c r="P2" s="66" t="s">
@@ -6101,15 +6017,15 @@
         <v>9</v>
       </c>
       <c r="T2" s="30" t="str">
-        <f>SUBSTITUTE(C2, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>De Materialidade</v>
       </c>
       <c r="U2" s="30" t="str">
-        <f>SUBSTITUTE(D2, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materialidades</v>
       </c>
       <c r="V2" s="30" t="str">
-        <f>SUBSTITUTE(E2, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materiais</v>
       </c>
       <c r="W2" s="30" t="s">
@@ -6173,19 +6089,19 @@
         <v>9</v>
       </c>
       <c r="L3" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", C3), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>De Materialidade</v>
       </c>
       <c r="M3" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", D3), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materialidades</v>
       </c>
       <c r="N3" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", E3), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Materiais</v>
       </c>
       <c r="O3" s="33" t="str">
-        <f>SUBSTITUTE(CONCATENATE("", F3), ".", " ")</f>
+        <f t="shared" si="0"/>
         <v>Tubo Multicamada</v>
       </c>
       <c r="P3" s="66" t="s">
@@ -6201,15 +6117,15 @@
         <v>9</v>
       </c>
       <c r="T3" s="30" t="str">
-        <f>SUBSTITUTE(C3, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>De Materialidade</v>
       </c>
       <c r="U3" s="30" t="str">
-        <f>SUBSTITUTE(D3, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materialidades</v>
       </c>
       <c r="V3" s="30" t="str">
-        <f>SUBSTITUTE(E3, ".", " ")</f>
+        <f t="shared" si="1"/>
         <v>Materiais</v>
       </c>
       <c r="W3" s="30" t="s">
@@ -6242,17 +6158,17 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:AD3">
     <sortCondition ref="F1:F3"/>
   </sortState>
-  <conditionalFormatting sqref="Y1:Y3 AA1:AA3 AC1:AC3 R1:R3 A1:B3">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+  <conditionalFormatting sqref="A1:B3 R1:R3 Y1:Y3 AA1:AA3 AC1:AC3">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F3">
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6467,7 +6383,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6804,7 +6720,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="19" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1495"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6874,22 +6790,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="17" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
